--- a/research/traditional_assets/database/data/zimbabwe/zimbabwe_building_materials.xlsx
+++ b/research/traditional_assets/database/data/zimbabwe/zimbabwe_building_materials.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1963287823985727</v>
+        <v>0.1956708816601777</v>
       </c>
       <c r="C2">
-        <v>2.094071070830501</v>
+        <v>2.077107884178736</v>
       </c>
       <c r="D2">
-        <v>1.826071070830501</v>
+        <v>1.830127884178736</v>
       </c>
       <c r="E2">
-        <v>-0.912</v>
+        <v>-0.89098</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.02102</v>
       </c>
       <c r="G2">
         <v>0.268</v>
@@ -1445,28 +1445,28 @@
         <v>0.93</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.001057306</v>
       </c>
       <c r="N2">
-        <v>0.93</v>
+        <v>0.9289426940000001</v>
       </c>
       <c r="O2">
-        <v>0.3255</v>
+        <v>0.3251299429</v>
       </c>
       <c r="P2">
-        <v>0.6045</v>
+        <v>0.6038127511</v>
       </c>
       <c r="Q2">
-        <v>1.4845</v>
+        <v>1.4838127511</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1963287823985727</v>
+        <v>0.1973171026870482</v>
       </c>
       <c r="T2">
-        <v>0.920615294616134</v>
+        <v>0.9266597384696744</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>879.593986982009</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1956708816601777</v>
+        <v>0.1950129809217827</v>
       </c>
       <c r="C3">
-        <v>2.077107884178736</v>
+        <v>2.060162762955905</v>
       </c>
       <c r="D3">
-        <v>1.830127884178736</v>
+        <v>1.834202762955905</v>
       </c>
       <c r="E3">
-        <v>-0.89098</v>
+        <v>-0.8699600000000001</v>
       </c>
       <c r="F3">
-        <v>0.02102</v>
+        <v>0.04204</v>
       </c>
       <c r="G3">
         <v>0.268</v>
@@ -1527,28 +1527,28 @@
         <v>0.93</v>
       </c>
       <c r="M3">
-        <v>0.001057306</v>
+        <v>0.002114612</v>
       </c>
       <c r="N3">
-        <v>0.9289426940000001</v>
+        <v>0.9278853880000001</v>
       </c>
       <c r="O3">
-        <v>0.3251299429</v>
+        <v>0.3247598858</v>
       </c>
       <c r="P3">
-        <v>0.6038127511</v>
+        <v>0.6031255022000001</v>
       </c>
       <c r="Q3">
-        <v>1.4838127511</v>
+        <v>1.4831255022</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1973171026870482</v>
+        <v>0.1983255927773293</v>
       </c>
       <c r="T3">
-        <v>0.9266597384696744</v>
+        <v>0.9328275383202256</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>879.593986982009</v>
+        <v>439.7969934910045</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1950129809217827</v>
+        <v>0.1943550801833877</v>
       </c>
       <c r="C4">
-        <v>2.060162762955905</v>
+        <v>2.043235828102254</v>
       </c>
       <c r="D4">
-        <v>1.834202762955905</v>
+        <v>1.838295828102254</v>
       </c>
       <c r="E4">
-        <v>-0.8699600000000001</v>
+        <v>-0.84894</v>
       </c>
       <c r="F4">
-        <v>0.04204</v>
+        <v>0.06305999999999999</v>
       </c>
       <c r="G4">
         <v>0.268</v>
@@ -1609,28 +1609,28 @@
         <v>0.93</v>
       </c>
       <c r="M4">
-        <v>0.002114612</v>
+        <v>0.003171917999999999</v>
       </c>
       <c r="N4">
-        <v>0.9278853880000001</v>
+        <v>0.926828082</v>
       </c>
       <c r="O4">
-        <v>0.3247598858</v>
+        <v>0.3243898287</v>
       </c>
       <c r="P4">
-        <v>0.6031255022000001</v>
+        <v>0.6024382533</v>
       </c>
       <c r="Q4">
-        <v>1.4831255022</v>
+        <v>1.4824382533</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1983255927773293</v>
+        <v>0.1993548764777192</v>
       </c>
       <c r="T4">
-        <v>0.9328275383202256</v>
+        <v>0.939122509301716</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>439.7969934910045</v>
+        <v>293.1979956606697</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1943550801833877</v>
+        <v>0.1936971794449927</v>
       </c>
       <c r="C5">
-        <v>2.043235828102254</v>
+        <v>2.026327201639965</v>
       </c>
       <c r="D5">
-        <v>1.838295828102254</v>
+        <v>1.842407201639966</v>
       </c>
       <c r="E5">
-        <v>-0.84894</v>
+        <v>-0.82792</v>
       </c>
       <c r="F5">
-        <v>0.06305999999999999</v>
+        <v>0.08408</v>
       </c>
       <c r="G5">
         <v>0.268</v>
@@ -1691,28 +1691,28 @@
         <v>0.93</v>
       </c>
       <c r="M5">
-        <v>0.003171917999999999</v>
+        <v>0.004229224</v>
       </c>
       <c r="N5">
-        <v>0.926828082</v>
+        <v>0.925770776</v>
       </c>
       <c r="O5">
-        <v>0.3243898287</v>
+        <v>0.3240197716</v>
       </c>
       <c r="P5">
-        <v>0.6024382533</v>
+        <v>0.6017510044000001</v>
       </c>
       <c r="Q5">
-        <v>1.4824382533</v>
+        <v>1.4817510044</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1993548764777192</v>
+        <v>0.200405603588534</v>
       </c>
       <c r="T5">
-        <v>0.939122509301716</v>
+        <v>0.9455486255119876</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>293.1979956606697</v>
+        <v>219.8984967455023</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1936971794449927</v>
+        <v>0.1930392787065977</v>
       </c>
       <c r="C6">
-        <v>2.026327201639965</v>
+        <v>2.009437006685287</v>
       </c>
       <c r="D6">
-        <v>1.842407201639966</v>
+        <v>1.846537006685288</v>
       </c>
       <c r="E6">
-        <v>-0.82792</v>
+        <v>-0.8069000000000001</v>
       </c>
       <c r="F6">
-        <v>0.08408</v>
+        <v>0.1051</v>
       </c>
       <c r="G6">
         <v>0.268</v>
@@ -1773,28 +1773,28 @@
         <v>0.93</v>
       </c>
       <c r="M6">
-        <v>0.004229224</v>
+        <v>0.005286529999999999</v>
       </c>
       <c r="N6">
-        <v>0.925770776</v>
+        <v>0.92471347</v>
       </c>
       <c r="O6">
-        <v>0.3240197716</v>
+        <v>0.3236497145</v>
       </c>
       <c r="P6">
-        <v>0.6017510044000001</v>
+        <v>0.6010637555</v>
       </c>
       <c r="Q6">
-        <v>1.4817510044</v>
+        <v>1.4810637555</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.200405603588534</v>
+        <v>0.2014784512701028</v>
       </c>
       <c r="T6">
-        <v>0.9455486255119876</v>
+        <v>0.9521100283793176</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>219.8984967455023</v>
+        <v>175.9187973964018</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1930392787065977</v>
+        <v>0.1923813779682026</v>
       </c>
       <c r="C7">
-        <v>2.009437006685287</v>
+        <v>1.992565367460821</v>
       </c>
       <c r="D7">
-        <v>1.846537006685288</v>
+        <v>1.850685367460821</v>
       </c>
       <c r="E7">
-        <v>-0.8069000000000001</v>
+        <v>-0.78588</v>
       </c>
       <c r="F7">
-        <v>0.1051</v>
+        <v>0.12612</v>
       </c>
       <c r="G7">
         <v>0.268</v>
@@ -1855,28 +1855,28 @@
         <v>0.93</v>
       </c>
       <c r="M7">
-        <v>0.005286529999999999</v>
+        <v>0.006343836</v>
       </c>
       <c r="N7">
-        <v>0.92471347</v>
+        <v>0.9236561640000001</v>
       </c>
       <c r="O7">
-        <v>0.3236497145</v>
+        <v>0.3232796574</v>
       </c>
       <c r="P7">
-        <v>0.6010637555</v>
+        <v>0.6003765066000001</v>
       </c>
       <c r="Q7">
-        <v>1.4810637555</v>
+        <v>1.4803765066</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.2014784512701028</v>
+        <v>0.2025741254980879</v>
       </c>
       <c r="T7">
-        <v>0.9521100283793176</v>
+        <v>0.9588110355629736</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>175.9187973964018</v>
+        <v>146.5989978303348</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1923813779682026</v>
+        <v>0.1917234772298076</v>
       </c>
       <c r="C8">
-        <v>1.992565367460821</v>
+        <v>1.975712409307975</v>
       </c>
       <c r="D8">
-        <v>1.850685367460821</v>
+        <v>1.854852409307975</v>
       </c>
       <c r="E8">
-        <v>-0.78588</v>
+        <v>-0.7648600000000001</v>
       </c>
       <c r="F8">
-        <v>0.12612</v>
+        <v>0.14714</v>
       </c>
       <c r="G8">
         <v>0.268</v>
@@ -1937,28 +1937,28 @@
         <v>0.93</v>
       </c>
       <c r="M8">
-        <v>0.006343835999999999</v>
+        <v>0.007401141999999998</v>
       </c>
       <c r="N8">
-        <v>0.9236561640000001</v>
+        <v>0.9225988580000001</v>
       </c>
       <c r="O8">
-        <v>0.3232796574</v>
+        <v>0.3229096003</v>
       </c>
       <c r="P8">
-        <v>0.6003765066000001</v>
+        <v>0.5996892577000001</v>
       </c>
       <c r="Q8">
-        <v>1.4803765066</v>
+        <v>1.4796892577</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.2025741254980879</v>
+        <v>0.2036933626126964</v>
       </c>
       <c r="T8">
-        <v>0.9588110355629736</v>
+        <v>0.9656561504279986</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>146.5989978303349</v>
+        <v>125.6562838545728</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1917234772298076</v>
+        <v>0.1910655764914126</v>
       </c>
       <c r="C9">
-        <v>1.975712409307975</v>
+        <v>1.958878258699593</v>
       </c>
       <c r="D9">
-        <v>1.854852409307975</v>
+        <v>1.859038258699593</v>
       </c>
       <c r="E9">
-        <v>-0.7648600000000001</v>
+        <v>-0.7438400000000001</v>
       </c>
       <c r="F9">
-        <v>0.14714</v>
+        <v>0.16816</v>
       </c>
       <c r="G9">
         <v>0.268</v>
@@ -2019,28 +2019,28 @@
         <v>0.93</v>
       </c>
       <c r="M9">
-        <v>0.007401141999999999</v>
+        <v>0.008458448</v>
       </c>
       <c r="N9">
-        <v>0.9225988580000001</v>
+        <v>0.9215415520000001</v>
       </c>
       <c r="O9">
-        <v>0.3229096003</v>
+        <v>0.3225395432</v>
       </c>
       <c r="P9">
-        <v>0.5996892577000001</v>
+        <v>0.5990020088000001</v>
       </c>
       <c r="Q9">
-        <v>1.4796892577</v>
+        <v>1.4790020088</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.2036933626126964</v>
+        <v>0.2048369309689268</v>
       </c>
       <c r="T9">
-        <v>0.9656561504279986</v>
+        <v>0.9726500721379154</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>125.6562838545727</v>
+        <v>109.9492483727511</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1910655764914126</v>
+        <v>0.1904076757530176</v>
       </c>
       <c r="C10">
-        <v>1.958878258699593</v>
+        <v>1.942063043252745</v>
       </c>
       <c r="D10">
-        <v>1.859038258699593</v>
+        <v>1.863243043252745</v>
       </c>
       <c r="E10">
-        <v>-0.7438400000000001</v>
+        <v>-0.72282</v>
       </c>
       <c r="F10">
-        <v>0.16816</v>
+        <v>0.18918</v>
       </c>
       <c r="G10">
         <v>0.268</v>
@@ -2101,28 +2101,28 @@
         <v>0.93</v>
       </c>
       <c r="M10">
-        <v>0.008458448</v>
+        <v>0.009515754</v>
       </c>
       <c r="N10">
-        <v>0.9215415520000001</v>
+        <v>0.920484246</v>
       </c>
       <c r="O10">
-        <v>0.3225395432</v>
+        <v>0.3221694861</v>
       </c>
       <c r="P10">
-        <v>0.5990020088000001</v>
+        <v>0.5983147599</v>
       </c>
       <c r="Q10">
-        <v>1.4790020088</v>
+        <v>1.4783147599</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.2048369309689268</v>
+        <v>0.2060056326956238</v>
       </c>
       <c r="T10">
-        <v>0.9726500721379154</v>
+        <v>0.9797977064128854</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>109.9492483727511</v>
+        <v>97.73266522022323</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1904076757530176</v>
+        <v>0.1897497750146226</v>
       </c>
       <c r="C11">
-        <v>1.942063043252745</v>
+        <v>1.925266891741701</v>
       </c>
       <c r="D11">
-        <v>1.863243043252745</v>
+        <v>1.867466891741701</v>
       </c>
       <c r="E11">
-        <v>-0.72282</v>
+        <v>-0.7018000000000001</v>
       </c>
       <c r="F11">
-        <v>0.18918</v>
+        <v>0.2102</v>
       </c>
       <c r="G11">
         <v>0.268</v>
@@ -2183,28 +2183,28 @@
         <v>0.93</v>
       </c>
       <c r="M11">
-        <v>0.009515754</v>
+        <v>0.01057306</v>
       </c>
       <c r="N11">
-        <v>0.920484246</v>
+        <v>0.91942694</v>
       </c>
       <c r="O11">
-        <v>0.3221694861</v>
+        <v>0.321799429</v>
       </c>
       <c r="P11">
-        <v>0.5983147599</v>
+        <v>0.597627511</v>
       </c>
       <c r="Q11">
-        <v>1.4783147599</v>
+        <v>1.477627511</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.2060056326956238</v>
+        <v>0.2072003055718029</v>
       </c>
       <c r="T11">
-        <v>0.9797977064128854</v>
+        <v>0.987104177005077</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>97.73266522022323</v>
+        <v>87.95939869820091</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1897497750146226</v>
+        <v>0.1890918742762276</v>
       </c>
       <c r="C12">
-        <v>1.925266891741701</v>
+        <v>1.908489934111072</v>
       </c>
       <c r="D12">
-        <v>1.867466891741701</v>
+        <v>1.871709934111072</v>
       </c>
       <c r="E12">
-        <v>-0.7018</v>
+        <v>-0.6807800000000001</v>
       </c>
       <c r="F12">
-        <v>0.2102</v>
+        <v>0.23122</v>
       </c>
       <c r="G12">
         <v>0.268</v>
@@ -2265,28 +2265,28 @@
         <v>0.93</v>
       </c>
       <c r="M12">
-        <v>0.01057306</v>
+        <v>0.011630366</v>
       </c>
       <c r="N12">
-        <v>0.91942694</v>
+        <v>0.918369634</v>
       </c>
       <c r="O12">
-        <v>0.321799429</v>
+        <v>0.3214293719</v>
       </c>
       <c r="P12">
-        <v>0.597627511</v>
+        <v>0.5969402621000001</v>
       </c>
       <c r="Q12">
-        <v>1.477627511</v>
+        <v>1.4769402621</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.2072003055718029</v>
+        <v>0.2084218250294693</v>
       </c>
       <c r="T12">
-        <v>0.987104177005077</v>
+        <v>0.994574837947655</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>87.95939869820091</v>
+        <v>79.9630897256372</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1890918742762276</v>
+        <v>0.1884339735378326</v>
       </c>
       <c r="C13">
-        <v>1.908489934111072</v>
+        <v>1.891732301489143</v>
       </c>
       <c r="D13">
-        <v>1.871709934111072</v>
+        <v>1.875972301489143</v>
       </c>
       <c r="E13">
-        <v>-0.6807800000000001</v>
+        <v>-0.6597600000000001</v>
       </c>
       <c r="F13">
-        <v>0.23122</v>
+        <v>0.25224</v>
       </c>
       <c r="G13">
         <v>0.268</v>
@@ -2347,28 +2347,28 @@
         <v>0.93</v>
       </c>
       <c r="M13">
-        <v>0.011630366</v>
+        <v>0.012687672</v>
       </c>
       <c r="N13">
-        <v>0.918369634</v>
+        <v>0.9173123280000001</v>
       </c>
       <c r="O13">
-        <v>0.3214293719</v>
+        <v>0.3210593148</v>
       </c>
       <c r="P13">
-        <v>0.5969402621000001</v>
+        <v>0.5962530132000001</v>
       </c>
       <c r="Q13">
-        <v>1.4769402621</v>
+        <v>1.4762530132</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.2084218250294693</v>
+        <v>0.2096711062929916</v>
       </c>
       <c r="T13">
-        <v>0.994574837947655</v>
+        <v>1.002215286638928</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>79.9630897256372</v>
+        <v>73.29949891516743</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1884339735378326</v>
+        <v>0.1877760727994376</v>
       </c>
       <c r="C14">
-        <v>1.891732301489143</v>
+        <v>1.874994126201373</v>
       </c>
       <c r="D14">
-        <v>1.875972301489143</v>
+        <v>1.880254126201373</v>
       </c>
       <c r="E14">
-        <v>-0.6597600000000001</v>
+        <v>-0.6387400000000001</v>
       </c>
       <c r="F14">
-        <v>0.25224</v>
+        <v>0.27326</v>
       </c>
       <c r="G14">
         <v>0.268</v>
@@ -2429,28 +2429,28 @@
         <v>0.93</v>
       </c>
       <c r="M14">
-        <v>0.012687672</v>
+        <v>0.013744978</v>
       </c>
       <c r="N14">
-        <v>0.9173123280000001</v>
+        <v>0.9162550220000001</v>
       </c>
       <c r="O14">
-        <v>0.3210593148</v>
+        <v>0.3206892577</v>
       </c>
       <c r="P14">
-        <v>0.5962530132000001</v>
+        <v>0.5955657643000001</v>
       </c>
       <c r="Q14">
-        <v>1.4762530132</v>
+        <v>1.4755657643</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.2096711062929916</v>
+        <v>0.2109491066660202</v>
       </c>
       <c r="T14">
-        <v>1.002215286638928</v>
+        <v>1.01003137782885</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>73.29949891516743</v>
+        <v>67.66107592169301</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1877760727994376</v>
+        <v>0.1871181720610426</v>
       </c>
       <c r="C15">
-        <v>1.874994126201373</v>
+        <v>1.858275541784094</v>
       </c>
       <c r="D15">
-        <v>1.880254126201373</v>
+        <v>1.884555541784095</v>
       </c>
       <c r="E15">
-        <v>-0.6387400000000001</v>
+        <v>-0.61772</v>
       </c>
       <c r="F15">
-        <v>0.27326</v>
+        <v>0.29428</v>
       </c>
       <c r="G15">
         <v>0.268</v>
@@ -2511,28 +2511,28 @@
         <v>0.93</v>
       </c>
       <c r="M15">
-        <v>0.013744978</v>
+        <v>0.014802284</v>
       </c>
       <c r="N15">
-        <v>0.9162550220000001</v>
+        <v>0.915197716</v>
       </c>
       <c r="O15">
-        <v>0.3206892577</v>
+        <v>0.3203192006</v>
       </c>
       <c r="P15">
-        <v>0.5955657643000001</v>
+        <v>0.5948785154</v>
       </c>
       <c r="Q15">
-        <v>1.4755657643</v>
+        <v>1.4748785154</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.2109491066660202</v>
+        <v>0.2122568279779565</v>
       </c>
       <c r="T15">
-        <v>1.01003137782885</v>
+        <v>1.01802923858133</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>67.66107592169301</v>
+        <v>62.82814192728636</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1871181720610426</v>
+        <v>0.1864602713226476</v>
       </c>
       <c r="C16">
-        <v>1.858275541784094</v>
+        <v>1.841576682998396</v>
       </c>
       <c r="D16">
-        <v>1.884555541784095</v>
+        <v>1.888876682998396</v>
       </c>
       <c r="E16">
-        <v>-0.61772</v>
+        <v>-0.5967</v>
       </c>
       <c r="F16">
-        <v>0.29428</v>
+        <v>0.3153</v>
       </c>
       <c r="G16">
         <v>0.268</v>
@@ -2593,28 +2593,28 @@
         <v>0.93</v>
       </c>
       <c r="M16">
-        <v>0.014802284</v>
+        <v>0.01585959</v>
       </c>
       <c r="N16">
-        <v>0.915197716</v>
+        <v>0.91414041</v>
       </c>
       <c r="O16">
-        <v>0.3203192006</v>
+        <v>0.3199491435</v>
       </c>
       <c r="P16">
-        <v>0.5948785154</v>
+        <v>0.5941912665</v>
       </c>
       <c r="Q16">
-        <v>1.4748785154</v>
+        <v>1.4741912665</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.2122568279779565</v>
+        <v>0.2135953192031148</v>
       </c>
       <c r="T16">
-        <v>1.01802923858133</v>
+        <v>1.026215284292691</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>62.82814192728636</v>
+        <v>58.63959913213393</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1864602713226476</v>
+        <v>0.1858023705842526</v>
       </c>
       <c r="C17">
-        <v>1.841576682998396</v>
+        <v>1.824897685844194</v>
       </c>
       <c r="D17">
-        <v>1.888876682998396</v>
+        <v>1.893217685844194</v>
       </c>
       <c r="E17">
-        <v>-0.5967</v>
+        <v>-0.57568</v>
       </c>
       <c r="F17">
-        <v>0.3153</v>
+        <v>0.33632</v>
       </c>
       <c r="G17">
         <v>0.268</v>
@@ -2675,28 +2675,28 @@
         <v>0.93</v>
       </c>
       <c r="M17">
-        <v>0.01585959</v>
+        <v>0.016916896</v>
       </c>
       <c r="N17">
-        <v>0.91414041</v>
+        <v>0.913083104</v>
       </c>
       <c r="O17">
-        <v>0.3199491435</v>
+        <v>0.3195790864</v>
       </c>
       <c r="P17">
-        <v>0.5941912665</v>
+        <v>0.5935040176</v>
       </c>
       <c r="Q17">
-        <v>1.4741912665</v>
+        <v>1.4735040176</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.2135953192031148</v>
+        <v>0.2149656792669674</v>
       </c>
       <c r="T17">
-        <v>1.026215284292691</v>
+        <v>1.034596235854322</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>58.63959913213395</v>
+        <v>54.97462418637556</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1858023705842526</v>
+        <v>0.1851444698458576</v>
       </c>
       <c r="C18">
-        <v>1.824897685844194</v>
+        <v>1.808238687574495</v>
       </c>
       <c r="D18">
-        <v>1.893217685844194</v>
+        <v>1.897578687574495</v>
       </c>
       <c r="E18">
-        <v>-0.57568</v>
+        <v>-0.55466</v>
       </c>
       <c r="F18">
-        <v>0.33632</v>
+        <v>0.35734</v>
       </c>
       <c r="G18">
         <v>0.268</v>
@@ -2757,28 +2757,28 @@
         <v>0.93</v>
       </c>
       <c r="M18">
-        <v>0.016916896</v>
+        <v>0.017974202</v>
       </c>
       <c r="N18">
-        <v>0.913083104</v>
+        <v>0.9120257980000001</v>
       </c>
       <c r="O18">
-        <v>0.3195790864</v>
+        <v>0.3192090293</v>
       </c>
       <c r="P18">
-        <v>0.5935040176</v>
+        <v>0.5928167687000001</v>
       </c>
       <c r="Q18">
-        <v>1.4735040176</v>
+        <v>1.4728167687</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.2149656792669674</v>
+        <v>0.2163690600552501</v>
       </c>
       <c r="T18">
-        <v>1.034596235854322</v>
+        <v>1.043179138055993</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>54.97462418637556</v>
+        <v>51.74082276364759</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1851444698458576</v>
+        <v>0.1844865691074626</v>
       </c>
       <c r="C19">
-        <v>1.808238687574495</v>
+        <v>1.791599826709877</v>
       </c>
       <c r="D19">
-        <v>1.897578687574495</v>
+        <v>1.901959826709877</v>
       </c>
       <c r="E19">
-        <v>-0.55466</v>
+        <v>-0.53364</v>
       </c>
       <c r="F19">
-        <v>0.35734</v>
+        <v>0.37836</v>
       </c>
       <c r="G19">
         <v>0.268</v>
@@ -2839,28 +2839,28 @@
         <v>0.93</v>
       </c>
       <c r="M19">
-        <v>0.017974202</v>
+        <v>0.019031508</v>
       </c>
       <c r="N19">
-        <v>0.9120257980000001</v>
+        <v>0.9109684920000001</v>
       </c>
       <c r="O19">
-        <v>0.3192090293</v>
+        <v>0.3188389722</v>
       </c>
       <c r="P19">
-        <v>0.5928167687000001</v>
+        <v>0.5921295198000001</v>
       </c>
       <c r="Q19">
-        <v>1.4728167687</v>
+        <v>1.4721295198</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.2163690600552501</v>
+        <v>0.217806669643247</v>
       </c>
       <c r="T19">
-        <v>1.043179138055993</v>
+        <v>1.051971379335753</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>51.74082276364759</v>
+        <v>48.86633261011162</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1844865691074626</v>
+        <v>0.1838286683690676</v>
       </c>
       <c r="C20">
-        <v>1.791599826709877</v>
+        <v>1.774981243053138</v>
       </c>
       <c r="D20">
-        <v>1.901959826709877</v>
+        <v>1.906361243053137</v>
       </c>
       <c r="E20">
-        <v>-0.5336400000000001</v>
+        <v>-0.5126200000000001</v>
       </c>
       <c r="F20">
-        <v>0.37836</v>
+        <v>0.39938</v>
       </c>
       <c r="G20">
         <v>0.268</v>
@@ -2921,28 +2921,28 @@
         <v>0.93</v>
       </c>
       <c r="M20">
-        <v>0.019031508</v>
+        <v>0.020088814</v>
       </c>
       <c r="N20">
-        <v>0.9109684920000001</v>
+        <v>0.9099111860000001</v>
       </c>
       <c r="O20">
-        <v>0.3188389722</v>
+        <v>0.3184689151</v>
       </c>
       <c r="P20">
-        <v>0.5921295198000001</v>
+        <v>0.5914422709</v>
       </c>
       <c r="Q20">
-        <v>1.4721295198</v>
+        <v>1.4714422709</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.217806669643247</v>
+        <v>0.219279775764281</v>
       </c>
       <c r="T20">
-        <v>1.051971379335753</v>
+        <v>1.060980712992792</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>48.86633261011162</v>
+        <v>46.29442036747417</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1838286683690676</v>
+        <v>0.1831707676306726</v>
       </c>
       <c r="C21">
-        <v>1.774981243053138</v>
+        <v>1.758383077704178</v>
       </c>
       <c r="D21">
-        <v>1.906361243053137</v>
+        <v>1.910783077704178</v>
       </c>
       <c r="E21">
-        <v>-0.5126200000000001</v>
+        <v>-0.4916</v>
       </c>
       <c r="F21">
-        <v>0.39938</v>
+        <v>0.4204</v>
       </c>
       <c r="G21">
         <v>0.268</v>
@@ -3003,28 +3003,28 @@
         <v>0.93</v>
       </c>
       <c r="M21">
-        <v>0.020088814</v>
+        <v>0.02114612</v>
       </c>
       <c r="N21">
-        <v>0.9099111860000001</v>
+        <v>0.90885388</v>
       </c>
       <c r="O21">
-        <v>0.3184689151</v>
+        <v>0.318098858</v>
       </c>
       <c r="P21">
-        <v>0.5914422709</v>
+        <v>0.590755022</v>
       </c>
       <c r="Q21">
-        <v>1.4714422709</v>
+        <v>1.470755022</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.219279775764281</v>
+        <v>0.2207897095383407</v>
       </c>
       <c r="T21">
-        <v>1.060980712992792</v>
+        <v>1.070215279991256</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>46.29442036747417</v>
+        <v>43.97969934910046</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1831707676306726</v>
+        <v>0.1825128668922776</v>
       </c>
       <c r="C22">
-        <v>1.758383077704178</v>
+        <v>1.741805473075077</v>
       </c>
       <c r="D22">
-        <v>1.910783077704178</v>
+        <v>1.915225473075077</v>
       </c>
       <c r="E22">
-        <v>-0.4916</v>
+        <v>-0.47058</v>
       </c>
       <c r="F22">
-        <v>0.4204</v>
+        <v>0.44142</v>
       </c>
       <c r="G22">
         <v>0.268</v>
@@ -3085,28 +3085,28 @@
         <v>0.93</v>
       </c>
       <c r="M22">
-        <v>0.02114612</v>
+        <v>0.022203426</v>
       </c>
       <c r="N22">
-        <v>0.90885388</v>
+        <v>0.907796574</v>
       </c>
       <c r="O22">
-        <v>0.318098858</v>
+        <v>0.3177288009</v>
       </c>
       <c r="P22">
-        <v>0.590755022</v>
+        <v>0.5900677731</v>
       </c>
       <c r="Q22">
-        <v>1.470755022</v>
+        <v>1.4700677731</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.2207897095383407</v>
+        <v>0.2223378694838957</v>
       </c>
       <c r="T22">
-        <v>1.070215279991256</v>
+        <v>1.07968363349601</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>43.97969934910046</v>
+        <v>41.88542795152424</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1825128668922776</v>
+        <v>0.1818549661538826</v>
       </c>
       <c r="C23">
-        <v>1.741805473075077</v>
+        <v>1.725248572905377</v>
       </c>
       <c r="D23">
-        <v>1.915225473075077</v>
+        <v>1.919688572905377</v>
       </c>
       <c r="E23">
-        <v>-0.4705800000000001</v>
+        <v>-0.4495600000000001</v>
       </c>
       <c r="F23">
-        <v>0.44142</v>
+        <v>0.46244</v>
       </c>
       <c r="G23">
         <v>0.268</v>
@@ -3167,28 +3167,28 @@
         <v>0.93</v>
       </c>
       <c r="M23">
-        <v>0.022203426</v>
+        <v>0.023260732</v>
       </c>
       <c r="N23">
-        <v>0.907796574</v>
+        <v>0.906739268</v>
       </c>
       <c r="O23">
-        <v>0.3177288009</v>
+        <v>0.3173587438</v>
       </c>
       <c r="P23">
-        <v>0.5900677731</v>
+        <v>0.5893805242000001</v>
       </c>
       <c r="Q23">
-        <v>1.4700677731</v>
+        <v>1.4693805242</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.2223378694838957</v>
+        <v>0.223925725838311</v>
       </c>
       <c r="T23">
-        <v>1.07968363349601</v>
+        <v>1.089394765295759</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>41.88542795152424</v>
+        <v>39.9815448628186</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1818549661538826</v>
+        <v>0.1811970654154876</v>
       </c>
       <c r="C24">
-        <v>1.725248572905377</v>
+        <v>1.708712522277591</v>
       </c>
       <c r="D24">
-        <v>1.919688572905377</v>
+        <v>1.924172522277591</v>
       </c>
       <c r="E24">
-        <v>-0.4495600000000001</v>
+        <v>-0.42854</v>
       </c>
       <c r="F24">
-        <v>0.46244</v>
+        <v>0.48346</v>
       </c>
       <c r="G24">
         <v>0.268</v>
@@ -3249,28 +3249,28 @@
         <v>0.93</v>
       </c>
       <c r="M24">
-        <v>0.023260732</v>
+        <v>0.024318038</v>
       </c>
       <c r="N24">
-        <v>0.906739268</v>
+        <v>0.9056819620000001</v>
       </c>
       <c r="O24">
-        <v>0.3173587438</v>
+        <v>0.3169886867</v>
       </c>
       <c r="P24">
-        <v>0.5893805242000001</v>
+        <v>0.5886932753</v>
       </c>
       <c r="Q24">
-        <v>1.4693805242</v>
+        <v>1.4686932753</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.223925725838311</v>
+        <v>0.2255548252149189</v>
       </c>
       <c r="T24">
-        <v>1.089394765295759</v>
+        <v>1.099358134285111</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>39.9815448628186</v>
+        <v>38.24321682530474</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1811970654154876</v>
+        <v>0.1805391646770926</v>
       </c>
       <c r="C25">
-        <v>1.708712522277591</v>
+        <v>1.692197467632925</v>
       </c>
       <c r="D25">
-        <v>1.924172522277591</v>
+        <v>1.928677467632925</v>
       </c>
       <c r="E25">
-        <v>-0.42854</v>
+        <v>-0.40752</v>
       </c>
       <c r="F25">
-        <v>0.48346</v>
+        <v>0.50448</v>
       </c>
       <c r="G25">
         <v>0.268</v>
@@ -3331,28 +3331,28 @@
         <v>0.93</v>
       </c>
       <c r="M25">
-        <v>0.024318038</v>
+        <v>0.025375344</v>
       </c>
       <c r="N25">
-        <v>0.9056819620000001</v>
+        <v>0.9046246560000001</v>
       </c>
       <c r="O25">
-        <v>0.3169886867</v>
+        <v>0.3166186296</v>
       </c>
       <c r="P25">
-        <v>0.5886932753</v>
+        <v>0.5880060264</v>
       </c>
       <c r="Q25">
-        <v>1.4686932753</v>
+        <v>1.4680060264</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2255548252149189</v>
+        <v>0.2272267956277534</v>
       </c>
       <c r="T25">
-        <v>1.099358134285111</v>
+        <v>1.109583697195235</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>38.24321682530474</v>
+        <v>36.64974945758371</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1805391646770926</v>
+        <v>0.1798812639386976</v>
       </c>
       <c r="C26">
-        <v>1.692197467632925</v>
+        <v>1.675703556787215</v>
       </c>
       <c r="D26">
-        <v>1.928677467632925</v>
+        <v>1.933203556787215</v>
       </c>
       <c r="E26">
-        <v>-0.4075200000000001</v>
+        <v>-0.3865000000000001</v>
       </c>
       <c r="F26">
-        <v>0.5044799999999999</v>
+        <v>0.5255</v>
       </c>
       <c r="G26">
         <v>0.268</v>
@@ -3413,28 +3413,28 @@
         <v>0.93</v>
       </c>
       <c r="M26">
-        <v>0.02537534399999999</v>
+        <v>0.02643265</v>
       </c>
       <c r="N26">
-        <v>0.9046246560000001</v>
+        <v>0.9035673500000001</v>
       </c>
       <c r="O26">
-        <v>0.3166186296</v>
+        <v>0.3162485725</v>
       </c>
       <c r="P26">
-        <v>0.5880060264</v>
+        <v>0.5873187775000002</v>
       </c>
       <c r="Q26">
-        <v>1.4680060264</v>
+        <v>1.4673187775</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2272267956277534</v>
+        <v>0.2289433519182634</v>
       </c>
       <c r="T26">
-        <v>1.109583697195235</v>
+        <v>1.120081941782963</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>36.64974945758372</v>
+        <v>35.18375947928037</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1798812639386976</v>
+        <v>0.1792233632003025</v>
       </c>
       <c r="C27">
-        <v>1.675703556787215</v>
+        <v>1.659230938947099</v>
       </c>
       <c r="D27">
-        <v>1.933203556787215</v>
+        <v>1.937750938947099</v>
       </c>
       <c r="E27">
-        <v>-0.3865000000000001</v>
+        <v>-0.36548</v>
       </c>
       <c r="F27">
-        <v>0.5255</v>
+        <v>0.54652</v>
       </c>
       <c r="G27">
         <v>0.268</v>
@@ -3495,28 +3495,28 @@
         <v>0.93</v>
       </c>
       <c r="M27">
-        <v>0.02643265</v>
+        <v>0.027489956</v>
       </c>
       <c r="N27">
-        <v>0.9035673500000001</v>
+        <v>0.902510044</v>
       </c>
       <c r="O27">
-        <v>0.3162485725</v>
+        <v>0.3158785154</v>
       </c>
       <c r="P27">
-        <v>0.5873187775000002</v>
+        <v>0.5866315286</v>
       </c>
       <c r="Q27">
-        <v>1.4673187775</v>
+        <v>1.4666315286</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2289433519182634</v>
+        <v>0.2307063016220305</v>
       </c>
       <c r="T27">
-        <v>1.120081941782963</v>
+        <v>1.1308639227109</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>35.18375947928037</v>
+        <v>33.8305379608465</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1792233632003025</v>
+        <v>0.1785654624619075</v>
       </c>
       <c r="C28">
-        <v>1.659230938947099</v>
+        <v>1.64277976472641</v>
       </c>
       <c r="D28">
-        <v>1.937750938947099</v>
+        <v>1.94231976472641</v>
       </c>
       <c r="E28">
-        <v>-0.36548</v>
+        <v>-0.34446</v>
       </c>
       <c r="F28">
-        <v>0.54652</v>
+        <v>0.56754</v>
       </c>
       <c r="G28">
         <v>0.268</v>
@@ -3577,28 +3577,28 @@
         <v>0.93</v>
       </c>
       <c r="M28">
-        <v>0.027489956</v>
+        <v>0.028547262</v>
       </c>
       <c r="N28">
-        <v>0.902510044</v>
+        <v>0.901452738</v>
       </c>
       <c r="O28">
-        <v>0.3158785154</v>
+        <v>0.3155084583</v>
       </c>
       <c r="P28">
-        <v>0.5866315286</v>
+        <v>0.5859442797000001</v>
       </c>
       <c r="Q28">
-        <v>1.4666315286</v>
+        <v>1.4659442797</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2307063016220305</v>
+        <v>0.2325175513176816</v>
       </c>
       <c r="T28">
-        <v>1.1308639227109</v>
+        <v>1.141941300376588</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>33.8305379608465</v>
+        <v>32.57755507340774</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1785654624619075</v>
+        <v>0.1779075617235125</v>
       </c>
       <c r="C29">
-        <v>1.64277976472641</v>
+        <v>1.626350186162809</v>
       </c>
       <c r="D29">
-        <v>1.94231976472641</v>
+        <v>1.94691018616281</v>
       </c>
       <c r="E29">
-        <v>-0.34446</v>
+        <v>-0.3234400000000001</v>
       </c>
       <c r="F29">
-        <v>0.56754</v>
+        <v>0.58856</v>
       </c>
       <c r="G29">
         <v>0.268</v>
@@ -3659,28 +3659,28 @@
         <v>0.93</v>
       </c>
       <c r="M29">
-        <v>0.028547262</v>
+        <v>0.029604568</v>
       </c>
       <c r="N29">
-        <v>0.901452738</v>
+        <v>0.9003954320000001</v>
       </c>
       <c r="O29">
-        <v>0.3155084583</v>
+        <v>0.3151384012</v>
       </c>
       <c r="P29">
-        <v>0.5859442797000001</v>
+        <v>0.5852570308</v>
       </c>
       <c r="Q29">
-        <v>1.4659442797</v>
+        <v>1.4652570308</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2325175513176816</v>
+        <v>0.2343791135048785</v>
       </c>
       <c r="T29">
-        <v>1.141941300376588</v>
+        <v>1.153326382977435</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>32.57755507340774</v>
+        <v>31.41407096364318</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1779075617235125</v>
+        <v>0.1772496609851175</v>
       </c>
       <c r="C30">
-        <v>1.626350186162809</v>
+        <v>1.609942356734645</v>
       </c>
       <c r="D30">
-        <v>1.94691018616281</v>
+        <v>1.951522356734645</v>
       </c>
       <c r="E30">
-        <v>-0.3234400000000001</v>
+        <v>-0.30242</v>
       </c>
       <c r="F30">
-        <v>0.58856</v>
+        <v>0.60958</v>
       </c>
       <c r="G30">
         <v>0.268</v>
@@ -3741,28 +3741,28 @@
         <v>0.93</v>
       </c>
       <c r="M30">
-        <v>0.029604568</v>
+        <v>0.030661874</v>
       </c>
       <c r="N30">
-        <v>0.9003954320000001</v>
+        <v>0.8993381260000001</v>
       </c>
       <c r="O30">
-        <v>0.3151384012</v>
+        <v>0.3147683441</v>
       </c>
       <c r="P30">
-        <v>0.5852570308</v>
+        <v>0.5845697819000001</v>
       </c>
       <c r="Q30">
-        <v>1.4652570308</v>
+        <v>1.4645697819</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2343791135048785</v>
+        <v>0.2362931140635459</v>
       </c>
       <c r="T30">
-        <v>1.153326382977435</v>
+        <v>1.165032172130418</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>31.41407096364318</v>
+        <v>30.33082713731066</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1772496609851175</v>
+        <v>0.1765917602467225</v>
       </c>
       <c r="C31">
-        <v>1.609942356734646</v>
+        <v>1.593556431378064</v>
       </c>
       <c r="D31">
-        <v>1.951522356734645</v>
+        <v>1.956156431378064</v>
       </c>
       <c r="E31">
-        <v>-0.3024200000000001</v>
+        <v>-0.2814000000000001</v>
       </c>
       <c r="F31">
-        <v>0.6095799999999999</v>
+        <v>0.6305999999999999</v>
       </c>
       <c r="G31">
         <v>0.268</v>
@@ -3823,28 +3823,28 @@
         <v>0.93</v>
       </c>
       <c r="M31">
-        <v>0.03066187399999999</v>
+        <v>0.03171917999999999</v>
       </c>
       <c r="N31">
-        <v>0.8993381260000001</v>
+        <v>0.8982808200000001</v>
       </c>
       <c r="O31">
-        <v>0.3147683441</v>
+        <v>0.314398287</v>
       </c>
       <c r="P31">
-        <v>0.5845697819000001</v>
+        <v>0.5838825330000001</v>
       </c>
       <c r="Q31">
-        <v>1.4645697819</v>
+        <v>1.463882533</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2362931140635459</v>
+        <v>0.2382618003524608</v>
       </c>
       <c r="T31">
-        <v>1.165032172130418</v>
+        <v>1.177072412402057</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>30.33082713731066</v>
+        <v>29.31979956606698</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1765917602467225</v>
+        <v>0.1759338595083275</v>
       </c>
       <c r="C32">
-        <v>1.593556431378064</v>
+        <v>1.577192566504355</v>
       </c>
       <c r="D32">
-        <v>1.956156431378064</v>
+        <v>1.960812566504355</v>
       </c>
       <c r="E32">
-        <v>-0.2814000000000001</v>
+        <v>-0.2603800000000001</v>
       </c>
       <c r="F32">
-        <v>0.6305999999999999</v>
+        <v>0.65162</v>
       </c>
       <c r="G32">
         <v>0.268</v>
@@ -3905,28 +3905,28 @@
         <v>0.93</v>
       </c>
       <c r="M32">
-        <v>0.03171917999999999</v>
+        <v>0.032776486</v>
       </c>
       <c r="N32">
-        <v>0.8982808200000001</v>
+        <v>0.897223514</v>
       </c>
       <c r="O32">
-        <v>0.314398287</v>
+        <v>0.3140282299</v>
       </c>
       <c r="P32">
-        <v>0.5838825330000001</v>
+        <v>0.5831952841000001</v>
       </c>
       <c r="Q32">
-        <v>1.463882533</v>
+        <v>1.4631952841</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2382618003524608</v>
+        <v>0.2402875500120689</v>
       </c>
       <c r="T32">
-        <v>1.177072412402057</v>
+        <v>1.189461645145338</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>29.31979956606698</v>
+        <v>28.3739995800648</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1759338595083275</v>
+        <v>0.1752759587699325</v>
       </c>
       <c r="C33">
-        <v>1.577192566504355</v>
+        <v>1.560850920017551</v>
       </c>
       <c r="D33">
-        <v>1.960812566504355</v>
+        <v>1.965490920017551</v>
       </c>
       <c r="E33">
-        <v>-0.2603800000000001</v>
+        <v>-0.23936</v>
       </c>
       <c r="F33">
-        <v>0.65162</v>
+        <v>0.67264</v>
       </c>
       <c r="G33">
         <v>0.268</v>
@@ -3987,28 +3987,28 @@
         <v>0.93</v>
       </c>
       <c r="M33">
-        <v>0.032776486</v>
+        <v>0.033833792</v>
       </c>
       <c r="N33">
-        <v>0.897223514</v>
+        <v>0.896166208</v>
       </c>
       <c r="O33">
-        <v>0.3140282299</v>
+        <v>0.3136581728</v>
       </c>
       <c r="P33">
-        <v>0.5831952841000001</v>
+        <v>0.5825080352000001</v>
       </c>
       <c r="Q33">
-        <v>1.4631952841</v>
+        <v>1.4625080352</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2402875500120689</v>
+        <v>0.2423728805440184</v>
       </c>
       <c r="T33">
-        <v>1.189461645145338</v>
+        <v>1.202215267086951</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>28.3739995800648</v>
+        <v>27.48731209318778</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1752759587699325</v>
+        <v>0.1746180580315375</v>
       </c>
       <c r="C34">
-        <v>1.560850920017551</v>
+        <v>1.544531651332279</v>
       </c>
       <c r="D34">
-        <v>1.965490920017551</v>
+        <v>1.970191651332279</v>
       </c>
       <c r="E34">
-        <v>-0.23936</v>
+        <v>-0.2183400000000001</v>
       </c>
       <c r="F34">
-        <v>0.67264</v>
+        <v>0.6936599999999999</v>
       </c>
       <c r="G34">
         <v>0.268</v>
@@ -4069,28 +4069,28 @@
         <v>0.93</v>
       </c>
       <c r="M34">
-        <v>0.033833792</v>
+        <v>0.034891098</v>
       </c>
       <c r="N34">
-        <v>0.896166208</v>
+        <v>0.895108902</v>
       </c>
       <c r="O34">
-        <v>0.3136581728</v>
+        <v>0.3132881157</v>
       </c>
       <c r="P34">
-        <v>0.5825080352000001</v>
+        <v>0.5818207863</v>
       </c>
       <c r="Q34">
-        <v>1.4625080352</v>
+        <v>1.4618207863</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2423728805440184</v>
+        <v>0.2445204597485635</v>
       </c>
       <c r="T34">
-        <v>1.202215267086951</v>
+        <v>1.21534959416115</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>27.48731209318778</v>
+        <v>26.65436324187906</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1746180580315375</v>
+        <v>0.1739601572931425</v>
       </c>
       <c r="C35">
-        <v>1.544531651332279</v>
+        <v>1.528234921391868</v>
       </c>
       <c r="D35">
-        <v>1.970191651332279</v>
+        <v>1.974914921391868</v>
       </c>
       <c r="E35">
-        <v>-0.2183400000000001</v>
+        <v>-0.1973200000000001</v>
       </c>
       <c r="F35">
-        <v>0.6936599999999999</v>
+        <v>0.71468</v>
       </c>
       <c r="G35">
         <v>0.268</v>
@@ -4151,28 +4151,28 @@
         <v>0.93</v>
       </c>
       <c r="M35">
-        <v>0.034891098</v>
+        <v>0.035948404</v>
       </c>
       <c r="N35">
-        <v>0.895108902</v>
+        <v>0.8940515960000001</v>
       </c>
       <c r="O35">
-        <v>0.3132881157</v>
+        <v>0.3129180586</v>
       </c>
       <c r="P35">
-        <v>0.5818207863</v>
+        <v>0.5811335374000001</v>
       </c>
       <c r="Q35">
-        <v>1.4618207863</v>
+        <v>1.4611335374</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2445204597485635</v>
+        <v>0.246733117110822</v>
       </c>
       <c r="T35">
-        <v>1.21534959416115</v>
+        <v>1.228881931146688</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>26.65436324187906</v>
+        <v>25.8704113818238</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1739601572931425</v>
+        <v>0.1733022565547475</v>
       </c>
       <c r="C36">
-        <v>1.528234921391868</v>
+        <v>1.511960892686712</v>
       </c>
       <c r="D36">
-        <v>1.974914921391868</v>
+        <v>1.979660892686712</v>
       </c>
       <c r="E36">
-        <v>-0.1973200000000001</v>
+        <v>-0.1763</v>
       </c>
       <c r="F36">
-        <v>0.71468</v>
+        <v>0.7357</v>
       </c>
       <c r="G36">
         <v>0.268</v>
@@ -4233,28 +4233,28 @@
         <v>0.93</v>
       </c>
       <c r="M36">
-        <v>0.035948404</v>
+        <v>0.03700571</v>
       </c>
       <c r="N36">
-        <v>0.8940515960000001</v>
+        <v>0.8929942900000001</v>
       </c>
       <c r="O36">
-        <v>0.3129180586</v>
+        <v>0.3125480015</v>
       </c>
       <c r="P36">
-        <v>0.5811335374000001</v>
+        <v>0.5804462885000001</v>
       </c>
       <c r="Q36">
-        <v>1.4611335374</v>
+        <v>1.4604462885</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.246733117110822</v>
+        <v>0.2490138562380731</v>
       </c>
       <c r="T36">
-        <v>1.228881931146688</v>
+        <v>1.242830647731781</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>25.8704113818238</v>
+        <v>25.13125677091455</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1733022565547475</v>
+        <v>0.1726443558163525</v>
       </c>
       <c r="C37">
-        <v>1.511960892686712</v>
+        <v>1.495709729272912</v>
       </c>
       <c r="D37">
-        <v>1.979660892686712</v>
+        <v>1.984429729272911</v>
       </c>
       <c r="E37">
-        <v>-0.1763</v>
+        <v>-0.15528</v>
       </c>
       <c r="F37">
-        <v>0.7357</v>
+        <v>0.7567200000000001</v>
       </c>
       <c r="G37">
         <v>0.268</v>
@@ -4315,28 +4315,28 @@
         <v>0.93</v>
       </c>
       <c r="M37">
-        <v>0.03700571</v>
+        <v>0.038063016</v>
       </c>
       <c r="N37">
-        <v>0.8929942900000001</v>
+        <v>0.8919369840000001</v>
       </c>
       <c r="O37">
-        <v>0.3125480015</v>
+        <v>0.3121779444</v>
       </c>
       <c r="P37">
-        <v>0.5804462885000001</v>
+        <v>0.5797590396000001</v>
       </c>
       <c r="Q37">
-        <v>1.4604462885</v>
+        <v>1.4597590396</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2490138562380731</v>
+        <v>0.2513658684630508</v>
       </c>
       <c r="T37">
-        <v>1.242830647731781</v>
+        <v>1.257215261710158</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>25.13125677091455</v>
+        <v>24.43316630505581</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1726443558163525</v>
+        <v>0.1719864550779575</v>
       </c>
       <c r="C38">
-        <v>1.495709729272912</v>
+        <v>1.479481596791172</v>
       </c>
       <c r="D38">
-        <v>1.984429729272911</v>
+        <v>1.989221596791172</v>
       </c>
       <c r="E38">
-        <v>-0.1552800000000001</v>
+        <v>-0.13426</v>
       </c>
       <c r="F38">
-        <v>0.7567199999999999</v>
+        <v>0.77774</v>
       </c>
       <c r="G38">
         <v>0.268</v>
@@ -4397,28 +4397,28 @@
         <v>0.93</v>
       </c>
       <c r="M38">
-        <v>0.038063016</v>
+        <v>0.039120322</v>
       </c>
       <c r="N38">
-        <v>0.8919369840000001</v>
+        <v>0.890879678</v>
       </c>
       <c r="O38">
-        <v>0.3121779444</v>
+        <v>0.3118078873</v>
       </c>
       <c r="P38">
-        <v>0.5797590396000001</v>
+        <v>0.5790717907</v>
       </c>
       <c r="Q38">
-        <v>1.4597590396</v>
+        <v>1.4590717907</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2513658684630508</v>
+        <v>0.2537925477427897</v>
       </c>
       <c r="T38">
-        <v>1.257215261710158</v>
+        <v>1.272056530100547</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>24.43316630505581</v>
+        <v>23.77281045897322</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1719864550779575</v>
+        <v>0.1713285543395625</v>
       </c>
       <c r="C39">
-        <v>1.479481596791172</v>
+        <v>1.463276662485984</v>
       </c>
       <c r="D39">
-        <v>1.989221596791172</v>
+        <v>1.994036662485984</v>
       </c>
       <c r="E39">
-        <v>-0.13426</v>
+        <v>-0.1132400000000001</v>
       </c>
       <c r="F39">
-        <v>0.77774</v>
+        <v>0.7987599999999999</v>
       </c>
       <c r="G39">
         <v>0.268</v>
@@ -4479,28 +4479,28 @@
         <v>0.93</v>
       </c>
       <c r="M39">
-        <v>0.039120322</v>
+        <v>0.04017762799999999</v>
       </c>
       <c r="N39">
-        <v>0.890879678</v>
+        <v>0.889822372</v>
       </c>
       <c r="O39">
-        <v>0.3118078873</v>
+        <v>0.3114378302</v>
       </c>
       <c r="P39">
-        <v>0.5790717907</v>
+        <v>0.5783845418</v>
       </c>
       <c r="Q39">
-        <v>1.4590717907</v>
+        <v>1.4583845418</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2537925477427897</v>
+        <v>0.2562975069992943</v>
       </c>
       <c r="T39">
-        <v>1.272056530100547</v>
+        <v>1.287376549084174</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>23.77281045897322</v>
+        <v>23.14721018373708</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1713285543395625</v>
+        <v>0.1706706536011675</v>
       </c>
       <c r="C40">
-        <v>1.463276662485984</v>
+        <v>1.447095095225081</v>
       </c>
       <c r="D40">
-        <v>1.994036662485984</v>
+        <v>1.99887509522508</v>
       </c>
       <c r="E40">
-        <v>-0.1132400000000001</v>
+        <v>-0.09222000000000008</v>
       </c>
       <c r="F40">
-        <v>0.7987599999999999</v>
+        <v>0.81978</v>
       </c>
       <c r="G40">
         <v>0.268</v>
@@ -4561,28 +4561,28 @@
         <v>0.93</v>
       </c>
       <c r="M40">
-        <v>0.04017762799999999</v>
+        <v>0.04123493399999999</v>
       </c>
       <c r="N40">
-        <v>0.889822372</v>
+        <v>0.888765066</v>
       </c>
       <c r="O40">
-        <v>0.3114378302</v>
+        <v>0.3110677731</v>
       </c>
       <c r="P40">
-        <v>0.5783845418</v>
+        <v>0.5776972929</v>
       </c>
       <c r="Q40">
-        <v>1.4583845418</v>
+        <v>1.4576972929</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2562975069992943</v>
+        <v>0.2588845960674877</v>
       </c>
       <c r="T40">
-        <v>1.287376549084174</v>
+        <v>1.303198863772183</v>
       </c>
       <c r="U40">
         <v>0.0503</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>23.14721018373708</v>
+        <v>22.55369197389767</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1706706536011675</v>
+        <v>0.1700127528627725</v>
       </c>
       <c r="C41">
-        <v>1.447095095225081</v>
+        <v>1.430937065519178</v>
       </c>
       <c r="D41">
-        <v>1.99887509522508</v>
+        <v>2.003737065519179</v>
       </c>
       <c r="E41">
-        <v>-0.09222000000000008</v>
+        <v>-0.07120000000000004</v>
       </c>
       <c r="F41">
-        <v>0.81978</v>
+        <v>0.8408</v>
       </c>
       <c r="G41">
         <v>0.268</v>
@@ -4643,28 +4643,28 @@
         <v>0.93</v>
       </c>
       <c r="M41">
-        <v>0.04123493399999999</v>
+        <v>0.04229223999999999</v>
       </c>
       <c r="N41">
-        <v>0.888765066</v>
+        <v>0.8877077600000001</v>
       </c>
       <c r="O41">
-        <v>0.3110677731</v>
+        <v>0.310697716</v>
       </c>
       <c r="P41">
-        <v>0.5776972929</v>
+        <v>0.5770100440000001</v>
       </c>
       <c r="Q41">
-        <v>1.4576972929</v>
+        <v>1.457010044</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2588845960674877</v>
+        <v>0.2615579214379541</v>
       </c>
       <c r="T41">
-        <v>1.303198863772183</v>
+        <v>1.319548588949792</v>
       </c>
       <c r="U41">
         <v>0.0503</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>22.55369197389767</v>
+        <v>21.98984967455023</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1700127528627725</v>
+        <v>0.1693548521243775</v>
       </c>
       <c r="C42">
-        <v>1.430937065519178</v>
+        <v>1.414802745542009</v>
       </c>
       <c r="D42">
-        <v>2.003737065519179</v>
+        <v>2.008622745542009</v>
       </c>
       <c r="E42">
-        <v>-0.07120000000000004</v>
+        <v>-0.05018</v>
       </c>
       <c r="F42">
-        <v>0.8408</v>
+        <v>0.86182</v>
       </c>
       <c r="G42">
         <v>0.268</v>
@@ -4725,28 +4725,28 @@
         <v>0.93</v>
       </c>
       <c r="M42">
-        <v>0.04229223999999999</v>
+        <v>0.043349546</v>
       </c>
       <c r="N42">
-        <v>0.8877077600000001</v>
+        <v>0.8866504540000001</v>
       </c>
       <c r="O42">
-        <v>0.310697716</v>
+        <v>0.3103276589</v>
       </c>
       <c r="P42">
-        <v>0.5770100440000001</v>
+        <v>0.5763227951000001</v>
       </c>
       <c r="Q42">
-        <v>1.457010044</v>
+        <v>1.4563227951</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2615579214379541</v>
+        <v>0.2643218680074195</v>
       </c>
       <c r="T42">
-        <v>1.319548588949792</v>
+        <v>1.336452542099523</v>
       </c>
       <c r="U42">
         <v>0.0503</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>21.98984967455023</v>
+        <v>21.45351187760998</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1693548521243775</v>
+        <v>0.1686969513859825</v>
       </c>
       <c r="C43">
-        <v>1.414802745542009</v>
+        <v>1.398692309150642</v>
       </c>
       <c r="D43">
-        <v>2.008622745542009</v>
+        <v>2.013532309150643</v>
       </c>
       <c r="E43">
-        <v>-0.05018</v>
+        <v>-0.02915999999999996</v>
       </c>
       <c r="F43">
-        <v>0.86182</v>
+        <v>0.8828400000000001</v>
       </c>
       <c r="G43">
         <v>0.268</v>
@@ -4807,28 +4807,28 @@
         <v>0.93</v>
       </c>
       <c r="M43">
-        <v>0.043349546</v>
+        <v>0.044406852</v>
       </c>
       <c r="N43">
-        <v>0.8866504540000001</v>
+        <v>0.885593148</v>
       </c>
       <c r="O43">
-        <v>0.3103276589</v>
+        <v>0.3099576018</v>
       </c>
       <c r="P43">
-        <v>0.5763227951000001</v>
+        <v>0.5756355462</v>
       </c>
       <c r="Q43">
-        <v>1.4563227951</v>
+        <v>1.4556355462</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2643218680074195</v>
+        <v>0.2671811230792801</v>
       </c>
       <c r="T43">
-        <v>1.336452542099523</v>
+        <v>1.353939390185452</v>
       </c>
       <c r="U43">
         <v>0.0503</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>21.45351187760998</v>
+        <v>20.94271397576212</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1686969513859825</v>
+        <v>0.1680390506475875</v>
       </c>
       <c r="C44">
-        <v>1.398692309150642</v>
+        <v>1.382605931906107</v>
       </c>
       <c r="D44">
-        <v>2.013532309150642</v>
+        <v>2.018465931906107</v>
       </c>
       <c r="E44">
-        <v>-0.02916000000000007</v>
+        <v>-0.008140000000000147</v>
       </c>
       <c r="F44">
-        <v>0.88284</v>
+        <v>0.9038599999999999</v>
       </c>
       <c r="G44">
         <v>0.268</v>
@@ -4889,28 +4889,28 @@
         <v>0.93</v>
       </c>
       <c r="M44">
-        <v>0.044406852</v>
+        <v>0.04546415799999999</v>
       </c>
       <c r="N44">
-        <v>0.8855931480000001</v>
+        <v>0.884535842</v>
       </c>
       <c r="O44">
-        <v>0.3099576018</v>
+        <v>0.3095875447</v>
       </c>
       <c r="P44">
-        <v>0.5756355462</v>
+        <v>0.5749482973</v>
       </c>
       <c r="Q44">
-        <v>1.4556355462</v>
+        <v>1.4549482973</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2671811230792801</v>
+        <v>0.2701407028905043</v>
       </c>
       <c r="T44">
-        <v>1.353939390185452</v>
+        <v>1.372039811888431</v>
       </c>
       <c r="U44">
         <v>0.0503</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>20.94271397576212</v>
+        <v>20.45567411586068</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1680390506475875</v>
+        <v>0.1673811499091925</v>
       </c>
       <c r="C45">
-        <v>1.382605931906107</v>
+        <v>1.366543791094323</v>
       </c>
       <c r="D45">
-        <v>2.018465931906107</v>
+        <v>2.023423791094323</v>
       </c>
       <c r="E45">
-        <v>-0.008140000000000147</v>
+        <v>0.01287999999999989</v>
       </c>
       <c r="F45">
-        <v>0.9038599999999999</v>
+        <v>0.9248799999999999</v>
       </c>
       <c r="G45">
         <v>0.268</v>
@@ -4971,28 +4971,28 @@
         <v>0.93</v>
       </c>
       <c r="M45">
-        <v>0.04546415799999999</v>
+        <v>0.04652146399999999</v>
       </c>
       <c r="N45">
-        <v>0.884535842</v>
+        <v>0.883478536</v>
       </c>
       <c r="O45">
-        <v>0.3095875447</v>
+        <v>0.3092174876</v>
       </c>
       <c r="P45">
-        <v>0.5749482973</v>
+        <v>0.5742610484</v>
       </c>
       <c r="Q45">
-        <v>1.4549482973</v>
+        <v>1.4542610484</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2701407028905043</v>
+        <v>0.2732059819807008</v>
       </c>
       <c r="T45">
-        <v>1.372039811888431</v>
+        <v>1.390786677223659</v>
       </c>
       <c r="U45">
         <v>0.0503</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>20.45567411586068</v>
+        <v>19.9907724314093</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1673811499091925</v>
+        <v>0.1667232491707974</v>
       </c>
       <c r="C46">
-        <v>1.366543791094323</v>
+        <v>1.350506065747333</v>
       </c>
       <c r="D46">
-        <v>2.023423791094323</v>
+        <v>2.028406065747333</v>
       </c>
       <c r="E46">
-        <v>0.01287999999999989</v>
+        <v>0.03389999999999993</v>
       </c>
       <c r="F46">
-        <v>0.9248799999999999</v>
+        <v>0.9459</v>
       </c>
       <c r="G46">
         <v>0.268</v>
@@ -5053,28 +5053,28 @@
         <v>0.93</v>
       </c>
       <c r="M46">
-        <v>0.04652146399999999</v>
+        <v>0.04757876999999999</v>
       </c>
       <c r="N46">
-        <v>0.883478536</v>
+        <v>0.8824212300000001</v>
       </c>
       <c r="O46">
-        <v>0.3092174876</v>
+        <v>0.3088474305</v>
       </c>
       <c r="P46">
-        <v>0.5742610484</v>
+        <v>0.5735737995000001</v>
       </c>
       <c r="Q46">
-        <v>1.4542610484</v>
+        <v>1.4535737995</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2732059819807008</v>
+        <v>0.2763827257650863</v>
       </c>
       <c r="T46">
-        <v>1.390786677223659</v>
+        <v>1.410215246752896</v>
       </c>
       <c r="U46">
         <v>0.0503</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>19.9907724314093</v>
+        <v>19.54653304404465</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1667232491707974</v>
+        <v>0.1660653484324025</v>
       </c>
       <c r="C47">
-        <v>1.350506065747333</v>
+        <v>1.334492936664852</v>
       </c>
       <c r="D47">
-        <v>2.028406065747333</v>
+        <v>2.033412936664852</v>
       </c>
       <c r="E47">
-        <v>0.03389999999999993</v>
+        <v>0.05491999999999997</v>
       </c>
       <c r="F47">
-        <v>0.9459</v>
+        <v>0.96692</v>
       </c>
       <c r="G47">
         <v>0.268</v>
@@ -5135,28 +5135,28 @@
         <v>0.93</v>
       </c>
       <c r="M47">
-        <v>0.04757876999999999</v>
+        <v>0.048636076</v>
       </c>
       <c r="N47">
-        <v>0.8824212300000001</v>
+        <v>0.8813639240000001</v>
       </c>
       <c r="O47">
-        <v>0.3088474305</v>
+        <v>0.3084773734</v>
       </c>
       <c r="P47">
-        <v>0.5735737995000001</v>
+        <v>0.5728865506</v>
       </c>
       <c r="Q47">
-        <v>1.4535737995</v>
+        <v>1.4528865506</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2763827257650863</v>
+        <v>0.2796771267266713</v>
       </c>
       <c r="T47">
-        <v>1.410215246752896</v>
+        <v>1.430363392931364</v>
       </c>
       <c r="U47">
         <v>0.0503</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>19.54653304404465</v>
+        <v>19.12160841265237</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1660653484324025</v>
+        <v>0.1654074476940075</v>
       </c>
       <c r="C48">
-        <v>1.334492936664852</v>
+        <v>1.318504586436142</v>
       </c>
       <c r="D48">
-        <v>2.033412936664852</v>
+        <v>2.038444586436142</v>
       </c>
       <c r="E48">
-        <v>0.05491999999999997</v>
+        <v>0.07594000000000001</v>
       </c>
       <c r="F48">
-        <v>0.96692</v>
+        <v>0.98794</v>
       </c>
       <c r="G48">
         <v>0.268</v>
@@ -5217,28 +5217,28 @@
         <v>0.93</v>
       </c>
       <c r="M48">
-        <v>0.048636076</v>
+        <v>0.049693382</v>
       </c>
       <c r="N48">
-        <v>0.8813639240000001</v>
+        <v>0.8803066180000001</v>
       </c>
       <c r="O48">
-        <v>0.3084773734</v>
+        <v>0.3081073163</v>
       </c>
       <c r="P48">
-        <v>0.5728865506</v>
+        <v>0.5721993017000001</v>
       </c>
       <c r="Q48">
-        <v>1.4528865506</v>
+        <v>1.4521993017</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2796771267266713</v>
+        <v>0.2830958447056744</v>
       </c>
       <c r="T48">
-        <v>1.430363392931364</v>
+        <v>1.451271846512793</v>
       </c>
       <c r="U48">
         <v>0.0503</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>19.12160841265237</v>
+        <v>18.71476568046828</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1654074476940075</v>
+        <v>0.1647495469556124</v>
       </c>
       <c r="C49">
-        <v>1.318504586436142</v>
+        <v>1.302541199462206</v>
       </c>
       <c r="D49">
-        <v>2.038444586436142</v>
+        <v>2.043501199462206</v>
       </c>
       <c r="E49">
-        <v>0.07594000000000001</v>
+        <v>0.09696000000000005</v>
       </c>
       <c r="F49">
-        <v>0.98794</v>
+        <v>1.00896</v>
       </c>
       <c r="G49">
         <v>0.268</v>
@@ -5299,28 +5299,28 @@
         <v>0.93</v>
       </c>
       <c r="M49">
-        <v>0.049693382</v>
+        <v>0.050750688</v>
       </c>
       <c r="N49">
-        <v>0.8803066180000001</v>
+        <v>0.879249312</v>
       </c>
       <c r="O49">
-        <v>0.3081073163</v>
+        <v>0.3077372592</v>
       </c>
       <c r="P49">
-        <v>0.5721993017000001</v>
+        <v>0.5715120527999999</v>
       </c>
       <c r="Q49">
-        <v>1.4521993017</v>
+        <v>1.4515120528</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2830958447056744</v>
+        <v>0.2866460518377162</v>
       </c>
       <c r="T49">
-        <v>1.451271846512793</v>
+        <v>1.472984471385814</v>
       </c>
       <c r="U49">
         <v>0.0503</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>18.71476568046828</v>
+        <v>18.32487472879185</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1647495469556124</v>
+        <v>0.1640916462172175</v>
       </c>
       <c r="C50">
-        <v>1.302541199462207</v>
+        <v>1.286602961978313</v>
       </c>
       <c r="D50">
-        <v>2.043501199462206</v>
+        <v>2.048582961978313</v>
       </c>
       <c r="E50">
-        <v>0.09695999999999982</v>
+        <v>0.1179799999999999</v>
       </c>
       <c r="F50">
-        <v>1.00896</v>
+        <v>1.02998</v>
       </c>
       <c r="G50">
         <v>0.268</v>
@@ -5381,28 +5381,28 @@
         <v>0.93</v>
       </c>
       <c r="M50">
-        <v>0.05075068799999999</v>
+        <v>0.05180799399999999</v>
       </c>
       <c r="N50">
-        <v>0.879249312</v>
+        <v>0.878192006</v>
       </c>
       <c r="O50">
-        <v>0.3077372592</v>
+        <v>0.3073672021</v>
       </c>
       <c r="P50">
-        <v>0.5715120527999999</v>
+        <v>0.5708248039</v>
       </c>
       <c r="Q50">
-        <v>1.4515120528</v>
+        <v>1.4508248039</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2866460518377162</v>
+        <v>0.2903354827788578</v>
       </c>
       <c r="T50">
-        <v>1.472984471385814</v>
+        <v>1.495548571744053</v>
       </c>
       <c r="U50">
         <v>0.0503</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>18.32487472879186</v>
+        <v>17.95089769351039</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1640916462172175</v>
+        <v>0.1634337454788224</v>
       </c>
       <c r="C51">
-        <v>1.286602961978313</v>
+        <v>1.270690062076864</v>
       </c>
       <c r="D51">
-        <v>2.048582961978313</v>
+        <v>2.053690062076864</v>
       </c>
       <c r="E51">
-        <v>0.1179799999999999</v>
+        <v>0.1389999999999999</v>
       </c>
       <c r="F51">
-        <v>1.02998</v>
+        <v>1.051</v>
       </c>
       <c r="G51">
         <v>0.268</v>
@@ -5463,28 +5463,28 @@
         <v>0.93</v>
       </c>
       <c r="M51">
-        <v>0.05180799399999999</v>
+        <v>0.0528653</v>
       </c>
       <c r="N51">
-        <v>0.878192006</v>
+        <v>0.8771347</v>
       </c>
       <c r="O51">
-        <v>0.3073672021</v>
+        <v>0.306997145</v>
       </c>
       <c r="P51">
-        <v>0.5708248039</v>
+        <v>0.5701375550000001</v>
       </c>
       <c r="Q51">
-        <v>1.4508248039</v>
+        <v>1.450137555</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2903354827788578</v>
+        <v>0.2941724909576449</v>
       </c>
       <c r="T51">
-        <v>1.495548571744053</v>
+        <v>1.519015236116621</v>
       </c>
       <c r="U51">
         <v>0.0503</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>17.95089769351039</v>
+        <v>17.59187973964018</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1634337454788224</v>
+        <v>0.1627758447404274</v>
       </c>
       <c r="C52">
-        <v>1.270690062076864</v>
+        <v>1.2548026897306</v>
       </c>
       <c r="D52">
-        <v>2.053690062076864</v>
+        <v>2.0588226897306</v>
       </c>
       <c r="E52">
-        <v>0.1389999999999999</v>
+        <v>0.1600199999999999</v>
       </c>
       <c r="F52">
-        <v>1.051</v>
+        <v>1.07202</v>
       </c>
       <c r="G52">
         <v>0.268</v>
@@ -5545,28 +5545,28 @@
         <v>0.93</v>
       </c>
       <c r="M52">
-        <v>0.0528653</v>
+        <v>0.053922606</v>
       </c>
       <c r="N52">
-        <v>0.8771347</v>
+        <v>0.8760773940000001</v>
       </c>
       <c r="O52">
-        <v>0.306997145</v>
+        <v>0.3066270879</v>
       </c>
       <c r="P52">
-        <v>0.5701375550000001</v>
+        <v>0.5694503061</v>
       </c>
       <c r="Q52">
-        <v>1.450137555</v>
+        <v>1.4494503061</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2941724909576449</v>
+        <v>0.2981661117151581</v>
       </c>
       <c r="T52">
-        <v>1.519015236116621</v>
+        <v>1.543439723524804</v>
       </c>
       <c r="U52">
         <v>0.0503</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>17.59187973964018</v>
+        <v>17.24694092121586</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1627758447404274</v>
+        <v>0.1621179440020325</v>
       </c>
       <c r="C53">
-        <v>1.2548026897306</v>
+        <v>1.238941036816156</v>
       </c>
       <c r="D53">
-        <v>2.0588226897306</v>
+        <v>2.063981036816156</v>
       </c>
       <c r="E53">
-        <v>0.1600199999999999</v>
+        <v>0.18104</v>
       </c>
       <c r="F53">
-        <v>1.07202</v>
+        <v>1.09304</v>
       </c>
       <c r="G53">
         <v>0.268</v>
@@ -5627,28 +5627,28 @@
         <v>0.93</v>
       </c>
       <c r="M53">
-        <v>0.053922606</v>
+        <v>0.054979912</v>
       </c>
       <c r="N53">
-        <v>0.8760773940000001</v>
+        <v>0.8750200880000001</v>
       </c>
       <c r="O53">
-        <v>0.3066270879</v>
+        <v>0.3062570308</v>
       </c>
       <c r="P53">
-        <v>0.5694503061</v>
+        <v>0.5687630572000001</v>
       </c>
       <c r="Q53">
-        <v>1.4494503061</v>
+        <v>1.4487630572</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2981661117151581</v>
+        <v>0.3023261333375676</v>
       </c>
       <c r="T53">
-        <v>1.543439723524804</v>
+        <v>1.568881897908329</v>
       </c>
       <c r="U53">
         <v>0.0503</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>17.24694092121586</v>
+        <v>16.91526898042325</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1621179440020325</v>
+        <v>0.1614600432636374</v>
       </c>
       <c r="C54">
-        <v>1.238941036816156</v>
+        <v>1.223105297137973</v>
       </c>
       <c r="D54">
-        <v>2.063981036816156</v>
+        <v>2.069165297137972</v>
       </c>
       <c r="E54">
-        <v>0.18104</v>
+        <v>0.20206</v>
       </c>
       <c r="F54">
-        <v>1.09304</v>
+        <v>1.11406</v>
       </c>
       <c r="G54">
         <v>0.268</v>
@@ -5709,28 +5709,28 @@
         <v>0.93</v>
       </c>
       <c r="M54">
-        <v>0.054979912</v>
+        <v>0.056037218</v>
       </c>
       <c r="N54">
-        <v>0.8750200880000001</v>
+        <v>0.873962782</v>
       </c>
       <c r="O54">
-        <v>0.3062570308</v>
+        <v>0.3058869737</v>
       </c>
       <c r="P54">
-        <v>0.5687630572000001</v>
+        <v>0.5680758083</v>
       </c>
       <c r="Q54">
-        <v>1.4487630572</v>
+        <v>1.4480758083</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.3023261333375676</v>
+        <v>0.3066631771566754</v>
       </c>
       <c r="T54">
-        <v>1.568881897908329</v>
+        <v>1.5954067180103</v>
       </c>
       <c r="U54">
         <v>0.0503</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>16.91526898042325</v>
+        <v>16.5961129619247</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1614600432636374</v>
+        <v>0.1608021425252424</v>
       </c>
       <c r="C55">
-        <v>1.223105297137973</v>
+        <v>1.207295666452566</v>
       </c>
       <c r="D55">
-        <v>2.069165297137972</v>
+        <v>2.074375666452566</v>
       </c>
       <c r="E55">
-        <v>0.20206</v>
+        <v>0.2230800000000001</v>
       </c>
       <c r="F55">
-        <v>1.11406</v>
+        <v>1.13508</v>
       </c>
       <c r="G55">
         <v>0.268</v>
@@ -5791,28 +5791,28 @@
         <v>0.93</v>
       </c>
       <c r="M55">
-        <v>0.056037218</v>
+        <v>0.057094524</v>
       </c>
       <c r="N55">
-        <v>0.873962782</v>
+        <v>0.872905476</v>
       </c>
       <c r="O55">
-        <v>0.3058869737</v>
+        <v>0.3055169166</v>
       </c>
       <c r="P55">
-        <v>0.5680758083</v>
+        <v>0.5673885594000001</v>
       </c>
       <c r="Q55">
-        <v>1.4480758083</v>
+        <v>1.4473885594</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.3066631771566754</v>
+        <v>0.3111887880983532</v>
       </c>
       <c r="T55">
-        <v>1.5954067180103</v>
+        <v>1.623084791160184</v>
       </c>
       <c r="U55">
         <v>0.0503</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>16.5961129619247</v>
+        <v>16.28877753670387</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1608021425252424</v>
+        <v>0.1601442417868474</v>
       </c>
       <c r="C56">
-        <v>1.207295666452566</v>
+        <v>1.191512342493173</v>
       </c>
       <c r="D56">
-        <v>2.074375666452566</v>
+        <v>2.079612342493173</v>
       </c>
       <c r="E56">
-        <v>0.2230800000000001</v>
+        <v>0.2441000000000001</v>
       </c>
       <c r="F56">
-        <v>1.13508</v>
+        <v>1.1561</v>
       </c>
       <c r="G56">
         <v>0.268</v>
@@ -5873,28 +5873,28 @@
         <v>0.93</v>
       </c>
       <c r="M56">
-        <v>0.057094524</v>
+        <v>0.05815183</v>
       </c>
       <c r="N56">
-        <v>0.872905476</v>
+        <v>0.87184817</v>
       </c>
       <c r="O56">
-        <v>0.3055169166</v>
+        <v>0.3051468595</v>
       </c>
       <c r="P56">
-        <v>0.5673885594000001</v>
+        <v>0.5667013105000001</v>
       </c>
       <c r="Q56">
-        <v>1.4473885594</v>
+        <v>1.4467013105</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.3111887880983532</v>
+        <v>0.3159155373041054</v>
       </c>
       <c r="T56">
-        <v>1.623084791160184</v>
+        <v>1.651993000894507</v>
       </c>
       <c r="U56">
         <v>0.0503</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>16.28877753670387</v>
+        <v>15.99261794512744</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1601442417868474</v>
+        <v>0.1594863410484524</v>
       </c>
       <c r="C57">
-        <v>1.191512342493173</v>
+        <v>1.175755524994759</v>
       </c>
       <c r="D57">
-        <v>2.079612342493173</v>
+        <v>2.084875524994759</v>
       </c>
       <c r="E57">
-        <v>0.2441000000000001</v>
+        <v>0.2651199999999999</v>
       </c>
       <c r="F57">
-        <v>1.1561</v>
+        <v>1.17712</v>
       </c>
       <c r="G57">
         <v>0.268</v>
@@ -5955,28 +5955,28 @@
         <v>0.93</v>
       </c>
       <c r="M57">
-        <v>0.05815183</v>
+        <v>0.059209136</v>
       </c>
       <c r="N57">
-        <v>0.87184817</v>
+        <v>0.8707908640000001</v>
       </c>
       <c r="O57">
-        <v>0.3051468595</v>
+        <v>0.3047768024</v>
       </c>
       <c r="P57">
-        <v>0.5667013105000001</v>
+        <v>0.5660140616</v>
       </c>
       <c r="Q57">
-        <v>1.4467013105</v>
+        <v>1.4460140616</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.3159155373041054</v>
+        <v>0.3208571387464828</v>
       </c>
       <c r="T57">
-        <v>1.651993000894507</v>
+        <v>1.682215220162209</v>
       </c>
       <c r="U57">
         <v>0.0503</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>15.99261794512744</v>
+        <v>15.70703548182159</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1594863410484524</v>
+        <v>0.1588284403100574</v>
       </c>
       <c r="C58">
-        <v>1.175755524994759</v>
+        <v>1.160025415719414</v>
       </c>
       <c r="D58">
-        <v>2.084875524994759</v>
+        <v>2.090165415719414</v>
       </c>
       <c r="E58">
-        <v>0.2651199999999999</v>
+        <v>0.2861399999999999</v>
       </c>
       <c r="F58">
-        <v>1.17712</v>
+        <v>1.19814</v>
       </c>
       <c r="G58">
         <v>0.268</v>
@@ -6037,28 +6037,28 @@
         <v>0.93</v>
       </c>
       <c r="M58">
-        <v>0.059209136</v>
+        <v>0.060266442</v>
       </c>
       <c r="N58">
-        <v>0.8707908640000001</v>
+        <v>0.8697335580000001</v>
       </c>
       <c r="O58">
-        <v>0.3047768024</v>
+        <v>0.3044067453</v>
       </c>
       <c r="P58">
-        <v>0.5660140616</v>
+        <v>0.5653268127000001</v>
       </c>
       <c r="Q58">
-        <v>1.4460140616</v>
+        <v>1.4453268127</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.3208571387464828</v>
+        <v>0.3260285821164126</v>
       </c>
       <c r="T58">
-        <v>1.682215220162209</v>
+        <v>1.713843124047012</v>
       </c>
       <c r="U58">
         <v>0.0503</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>15.70703548182159</v>
+        <v>15.43147345582472</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1588284403100574</v>
+        <v>0.1581705395716624</v>
       </c>
       <c r="C59">
-        <v>1.160025415719414</v>
+        <v>1.144322218482138</v>
       </c>
       <c r="D59">
-        <v>2.090165415719414</v>
+        <v>2.095482218482138</v>
       </c>
       <c r="E59">
-        <v>0.2861399999999999</v>
+        <v>0.30716</v>
       </c>
       <c r="F59">
-        <v>1.19814</v>
+        <v>1.21916</v>
       </c>
       <c r="G59">
         <v>0.268</v>
@@ -6119,28 +6119,28 @@
         <v>0.93</v>
       </c>
       <c r="M59">
-        <v>0.060266442</v>
+        <v>0.061323748</v>
       </c>
       <c r="N59">
-        <v>0.8697335580000001</v>
+        <v>0.8686762520000001</v>
       </c>
       <c r="O59">
-        <v>0.3044067453</v>
+        <v>0.3040366882</v>
       </c>
       <c r="P59">
-        <v>0.5653268127000001</v>
+        <v>0.5646395638000001</v>
       </c>
       <c r="Q59">
-        <v>1.4453268127</v>
+        <v>1.4446395638</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.3260285821164126</v>
+        <v>0.3314462846944344</v>
       </c>
       <c r="T59">
-        <v>1.713843124047012</v>
+        <v>1.746977118592997</v>
       </c>
       <c r="U59">
         <v>0.0503</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>15.43147345582472</v>
+        <v>15.16541356865533</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1581705395716624</v>
+        <v>0.1575126388332674</v>
       </c>
       <c r="C60">
-        <v>1.144322218482139</v>
+        <v>1.128646139177016</v>
       </c>
       <c r="D60">
-        <v>2.095482218482138</v>
+        <v>2.100826139177016</v>
       </c>
       <c r="E60">
-        <v>0.3071599999999998</v>
+        <v>0.3281799999999998</v>
       </c>
       <c r="F60">
-        <v>1.21916</v>
+        <v>1.24018</v>
       </c>
       <c r="G60">
         <v>0.268</v>
@@ -6201,28 +6201,28 @@
         <v>0.93</v>
       </c>
       <c r="M60">
-        <v>0.06132374799999998</v>
+        <v>0.06238105399999999</v>
       </c>
       <c r="N60">
-        <v>0.8686762520000001</v>
+        <v>0.8676189460000001</v>
       </c>
       <c r="O60">
-        <v>0.3040366882</v>
+        <v>0.3036666311</v>
       </c>
       <c r="P60">
-        <v>0.5646395638000001</v>
+        <v>0.5639523149000001</v>
       </c>
       <c r="Q60">
-        <v>1.4446395638</v>
+        <v>1.4439523149</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.3314462846944343</v>
+        <v>0.3371282654469936</v>
       </c>
       <c r="T60">
-        <v>1.746977118592997</v>
+        <v>1.781727405555859</v>
       </c>
       <c r="U60">
         <v>0.0503</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>15.16541356865533</v>
+        <v>14.90837266071202</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1575126388332674</v>
+        <v>0.1568547380948724</v>
       </c>
       <c r="C61">
-        <v>1.128646139177016</v>
+        <v>1.112997385803794</v>
       </c>
       <c r="D61">
-        <v>2.100826139177016</v>
+        <v>2.106197385803794</v>
       </c>
       <c r="E61">
-        <v>0.3281799999999998</v>
+        <v>0.3491999999999998</v>
       </c>
       <c r="F61">
-        <v>1.24018</v>
+        <v>1.2612</v>
       </c>
       <c r="G61">
         <v>0.268</v>
@@ -6283,28 +6283,28 @@
         <v>0.93</v>
       </c>
       <c r="M61">
-        <v>0.06238105399999999</v>
+        <v>0.06343835999999999</v>
       </c>
       <c r="N61">
-        <v>0.8676189460000001</v>
+        <v>0.86656164</v>
       </c>
       <c r="O61">
-        <v>0.3036666311</v>
+        <v>0.303296574</v>
       </c>
       <c r="P61">
-        <v>0.5639523149000001</v>
+        <v>0.563265066</v>
       </c>
       <c r="Q61">
-        <v>1.4439523149</v>
+        <v>1.443265066</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.3371282654469936</v>
+        <v>0.343094345237181</v>
       </c>
       <c r="T61">
-        <v>1.781727405555859</v>
+        <v>1.818215206866864</v>
       </c>
       <c r="U61">
         <v>0.0503</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>14.90837266071202</v>
+        <v>14.65989978303349</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1568547380948724</v>
+        <v>0.1561968373564774</v>
       </c>
       <c r="C62">
-        <v>1.112997385803794</v>
+        <v>1.097376168494866</v>
       </c>
       <c r="D62">
-        <v>2.106197385803794</v>
+        <v>2.111596168494867</v>
       </c>
       <c r="E62">
-        <v>0.3491999999999998</v>
+        <v>0.3702199999999999</v>
       </c>
       <c r="F62">
-        <v>1.2612</v>
+        <v>1.28222</v>
       </c>
       <c r="G62">
         <v>0.268</v>
@@ -6365,28 +6365,28 @@
         <v>0.93</v>
       </c>
       <c r="M62">
-        <v>0.06343835999999999</v>
+        <v>0.06449566599999999</v>
       </c>
       <c r="N62">
-        <v>0.86656164</v>
+        <v>0.865504334</v>
       </c>
       <c r="O62">
-        <v>0.303296574</v>
+        <v>0.3029265169</v>
       </c>
       <c r="P62">
-        <v>0.563265066</v>
+        <v>0.5625778171</v>
       </c>
       <c r="Q62">
-        <v>1.443265066</v>
+        <v>1.4425778171</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.343094345237181</v>
+        <v>0.3493663778371215</v>
       </c>
       <c r="T62">
-        <v>1.818215206866864</v>
+        <v>1.85657417747587</v>
       </c>
       <c r="U62">
         <v>0.0503</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>14.65989978303349</v>
+        <v>14.41957355708212</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1561968373564774</v>
+        <v>0.1555389366180824</v>
       </c>
       <c r="C63">
-        <v>1.097376168494866</v>
+        <v>1.081782699542686</v>
       </c>
       <c r="D63">
-        <v>2.111596168494867</v>
+        <v>2.117022699542686</v>
       </c>
       <c r="E63">
-        <v>0.3702199999999999</v>
+        <v>0.3912399999999999</v>
       </c>
       <c r="F63">
-        <v>1.28222</v>
+        <v>1.30324</v>
       </c>
       <c r="G63">
         <v>0.268</v>
@@ -6447,28 +6447,28 @@
         <v>0.93</v>
       </c>
       <c r="M63">
-        <v>0.06449566599999999</v>
+        <v>0.065552972</v>
       </c>
       <c r="N63">
-        <v>0.865504334</v>
+        <v>0.8644470280000001</v>
       </c>
       <c r="O63">
-        <v>0.3029265169</v>
+        <v>0.3025564598</v>
       </c>
       <c r="P63">
-        <v>0.5625778171</v>
+        <v>0.5618905682000001</v>
       </c>
       <c r="Q63">
-        <v>1.4425778171</v>
+        <v>1.4418905682</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.3493663778371215</v>
+        <v>0.3559685174160064</v>
       </c>
       <c r="T63">
-        <v>1.85657417747587</v>
+        <v>1.896952041274824</v>
       </c>
       <c r="U63">
         <v>0.0503</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>14.41957355708212</v>
+        <v>14.1869997900324</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1555389366180824</v>
+        <v>0.1548810358796874</v>
       </c>
       <c r="C64">
-        <v>1.081782699542686</v>
+        <v>1.066217193427582</v>
       </c>
       <c r="D64">
-        <v>2.117022699542686</v>
+        <v>2.122477193427582</v>
       </c>
       <c r="E64">
-        <v>0.3912399999999999</v>
+        <v>0.41226</v>
       </c>
       <c r="F64">
-        <v>1.30324</v>
+        <v>1.32426</v>
       </c>
       <c r="G64">
         <v>0.268</v>
@@ -6529,28 +6529,28 @@
         <v>0.93</v>
       </c>
       <c r="M64">
-        <v>0.065552972</v>
+        <v>0.06661027799999999</v>
       </c>
       <c r="N64">
-        <v>0.8644470280000001</v>
+        <v>0.8633897220000001</v>
       </c>
       <c r="O64">
-        <v>0.3025564598</v>
+        <v>0.3021864027</v>
       </c>
       <c r="P64">
-        <v>0.5618905682000001</v>
+        <v>0.5612033193000001</v>
       </c>
       <c r="Q64">
-        <v>1.4418905682</v>
+        <v>1.4412033193</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3559685174160064</v>
+        <v>0.3629275294045605</v>
       </c>
       <c r="T64">
-        <v>1.896952041274824</v>
+        <v>1.939512492306152</v>
       </c>
       <c r="U64">
         <v>0.0503</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>14.1869997900324</v>
+        <v>13.96180931717475</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1548810358796874</v>
+        <v>0.1542231351412924</v>
       </c>
       <c r="C65">
-        <v>1.066217193427582</v>
+        <v>1.050679866846021</v>
       </c>
       <c r="D65">
-        <v>2.122477193427582</v>
+        <v>2.127959866846021</v>
       </c>
       <c r="E65">
-        <v>0.41226</v>
+        <v>0.43328</v>
       </c>
       <c r="F65">
-        <v>1.32426</v>
+        <v>1.34528</v>
       </c>
       <c r="G65">
         <v>0.268</v>
@@ -6611,28 +6611,28 @@
         <v>0.93</v>
       </c>
       <c r="M65">
-        <v>0.06661027799999999</v>
+        <v>0.067667584</v>
       </c>
       <c r="N65">
-        <v>0.8633897220000001</v>
+        <v>0.8623324160000001</v>
       </c>
       <c r="O65">
-        <v>0.3021864027</v>
+        <v>0.3018163456</v>
       </c>
       <c r="P65">
-        <v>0.5612033193000001</v>
+        <v>0.5605160704000001</v>
       </c>
       <c r="Q65">
-        <v>1.4412033193</v>
+        <v>1.4405160704</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3629275294045605</v>
+        <v>0.3702731531702567</v>
       </c>
       <c r="T65">
-        <v>1.939512492306152</v>
+        <v>1.984437412839223</v>
       </c>
       <c r="U65">
         <v>0.0503</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>13.96180931717475</v>
+        <v>13.74365604659389</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1542231351412924</v>
+        <v>0.1535652344028974</v>
       </c>
       <c r="C66">
-        <v>1.050679866846021</v>
+        <v>1.035170938739306</v>
       </c>
       <c r="D66">
-        <v>2.127959866846021</v>
+        <v>2.133470938739306</v>
       </c>
       <c r="E66">
-        <v>0.43328</v>
+        <v>0.4543</v>
       </c>
       <c r="F66">
-        <v>1.34528</v>
+        <v>1.3663</v>
       </c>
       <c r="G66">
         <v>0.268</v>
@@ -6693,28 +6693,28 @@
         <v>0.93</v>
       </c>
       <c r="M66">
-        <v>0.067667584</v>
+        <v>0.06872489</v>
       </c>
       <c r="N66">
-        <v>0.8623324160000001</v>
+        <v>0.86127511</v>
       </c>
       <c r="O66">
-        <v>0.3018163456</v>
+        <v>0.3014462885</v>
       </c>
       <c r="P66">
-        <v>0.5605160704000001</v>
+        <v>0.5598288215</v>
       </c>
       <c r="Q66">
-        <v>1.4405160704</v>
+        <v>1.4398288215</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3702731531702567</v>
+        <v>0.3780385268654211</v>
       </c>
       <c r="T66">
-        <v>1.984437412839223</v>
+        <v>2.031929471688467</v>
       </c>
       <c r="U66">
         <v>0.0503</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>13.74365604659389</v>
+        <v>13.5322151843386</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1535652344028974</v>
+        <v>0.1529073336645024</v>
       </c>
       <c r="C67">
-        <v>1.035170938739306</v>
+        <v>1.01969063032272</v>
       </c>
       <c r="D67">
-        <v>2.133470938739306</v>
+        <v>2.13901063032272</v>
       </c>
       <c r="E67">
-        <v>0.4543</v>
+        <v>0.4753199999999999</v>
       </c>
       <c r="F67">
-        <v>1.3663</v>
+        <v>1.38732</v>
       </c>
       <c r="G67">
         <v>0.268</v>
@@ -6775,28 +6775,28 @@
         <v>0.93</v>
       </c>
       <c r="M67">
-        <v>0.06872489</v>
+        <v>0.06978219599999999</v>
       </c>
       <c r="N67">
-        <v>0.86127511</v>
+        <v>0.860217804</v>
       </c>
       <c r="O67">
-        <v>0.3014462885</v>
+        <v>0.3010762314</v>
       </c>
       <c r="P67">
-        <v>0.5598288215</v>
+        <v>0.5591415726</v>
       </c>
       <c r="Q67">
-        <v>1.4398288215</v>
+        <v>1.4391415726</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3780385268654211</v>
+        <v>0.3862606872485364</v>
       </c>
       <c r="T67">
-        <v>2.031929471688467</v>
+        <v>2.082215181058256</v>
       </c>
       <c r="U67">
         <v>0.0503</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>13.5322151843386</v>
+        <v>13.32718162093953</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1529073336645024</v>
+        <v>0.1522494329261074</v>
       </c>
       <c r="C68">
-        <v>1.01969063032272</v>
+        <v>1.004239165115124</v>
       </c>
       <c r="D68">
-        <v>2.13901063032272</v>
+        <v>2.144579165115124</v>
       </c>
       <c r="E68">
-        <v>0.4753199999999999</v>
+        <v>0.4963399999999999</v>
       </c>
       <c r="F68">
-        <v>1.38732</v>
+        <v>1.40834</v>
       </c>
       <c r="G68">
         <v>0.268</v>
@@ -6857,28 +6857,28 @@
         <v>0.93</v>
       </c>
       <c r="M68">
-        <v>0.06978219599999999</v>
+        <v>0.070839502</v>
       </c>
       <c r="N68">
-        <v>0.860217804</v>
+        <v>0.8591604980000001</v>
       </c>
       <c r="O68">
-        <v>0.3010762314</v>
+        <v>0.3007061743</v>
       </c>
       <c r="P68">
-        <v>0.5591415726</v>
+        <v>0.5584543237</v>
       </c>
       <c r="Q68">
-        <v>1.4391415726</v>
+        <v>1.4384543237</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3862606872485364</v>
+        <v>0.3949811603821437</v>
       </c>
       <c r="T68">
-        <v>2.082215181058256</v>
+        <v>2.13554850917773</v>
       </c>
       <c r="U68">
         <v>0.0503</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>13.32718162093953</v>
+        <v>13.12826846241805</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1522494329261074</v>
+        <v>0.1515915321877124</v>
       </c>
       <c r="C69">
-        <v>1.004239165115124</v>
+        <v>0.9888167689690235</v>
       </c>
       <c r="D69">
-        <v>2.144579165115124</v>
+        <v>2.150176768969023</v>
       </c>
       <c r="E69">
-        <v>0.4963399999999999</v>
+        <v>0.5173599999999999</v>
       </c>
       <c r="F69">
-        <v>1.40834</v>
+        <v>1.42936</v>
       </c>
       <c r="G69">
         <v>0.268</v>
@@ -6939,28 +6939,28 @@
         <v>0.93</v>
       </c>
       <c r="M69">
-        <v>0.070839502</v>
+        <v>0.07189680799999999</v>
       </c>
       <c r="N69">
-        <v>0.8591604980000001</v>
+        <v>0.8581031920000001</v>
       </c>
       <c r="O69">
-        <v>0.3007061743</v>
+        <v>0.3003361172</v>
       </c>
       <c r="P69">
-        <v>0.5584543237</v>
+        <v>0.5577670748000001</v>
       </c>
       <c r="Q69">
-        <v>1.4384543237</v>
+        <v>1.4377670748</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3949811603821437</v>
+        <v>0.4042466630866012</v>
       </c>
       <c r="T69">
-        <v>2.13554850917773</v>
+        <v>2.19221517030467</v>
       </c>
       <c r="U69">
         <v>0.0503</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>13.12826846241805</v>
+        <v>12.9352056909119</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1515915321877124</v>
+        <v>0.1516063814493174</v>
       </c>
       <c r="C70">
-        <v>0.9888167689690235</v>
+        <v>0.9676701049852969</v>
       </c>
       <c r="D70">
-        <v>2.150176768969023</v>
+        <v>2.150050104985297</v>
       </c>
       <c r="E70">
-        <v>0.5173599999999999</v>
+        <v>0.53838</v>
       </c>
       <c r="F70">
-        <v>1.42936</v>
+        <v>1.45038</v>
       </c>
       <c r="G70">
         <v>0.268</v>
@@ -7021,45 +7021,45 @@
         <v>0.93</v>
       </c>
       <c r="M70">
-        <v>0.07189680799999999</v>
+        <v>0.075129684</v>
       </c>
       <c r="N70">
-        <v>0.8581031920000001</v>
+        <v>0.8548703160000001</v>
       </c>
       <c r="O70">
-        <v>0.3003361172</v>
+        <v>0.2992046106</v>
       </c>
       <c r="P70">
-        <v>0.5577670748000001</v>
+        <v>0.5556657054</v>
       </c>
       <c r="Q70">
-        <v>1.4377670748</v>
+        <v>1.4356657054</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.4042466630866012</v>
+        <v>0.4141099401590884</v>
       </c>
       <c r="T70">
-        <v>2.19221517030467</v>
+        <v>2.252537745052702</v>
       </c>
       <c r="U70">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V70">
         <v>0.35</v>
       </c>
       <c r="W70">
-        <v>0.032695</v>
+        <v>0.03367</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y70">
-        <v>12.9352056909119</v>
+        <v>12.37859592221897</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1516063814493174</v>
+        <v>0.1509582307109224</v>
       </c>
       <c r="C71">
-        <v>0.9676701049852969</v>
+        <v>0.9521927473000735</v>
       </c>
       <c r="D71">
-        <v>2.150050104985297</v>
+        <v>2.155592747300074</v>
       </c>
       <c r="E71">
-        <v>0.53838</v>
+        <v>0.5594</v>
       </c>
       <c r="F71">
-        <v>1.45038</v>
+        <v>1.4714</v>
       </c>
       <c r="G71">
         <v>0.268</v>
@@ -7103,28 +7103,28 @@
         <v>0.93</v>
       </c>
       <c r="M71">
-        <v>0.075129684</v>
+        <v>0.07621852</v>
       </c>
       <c r="N71">
-        <v>0.8548703160000001</v>
+        <v>0.8537814800000001</v>
       </c>
       <c r="O71">
-        <v>0.2992046106</v>
+        <v>0.298823518</v>
       </c>
       <c r="P71">
-        <v>0.5556657054</v>
+        <v>0.554957962</v>
       </c>
       <c r="Q71">
-        <v>1.4356657054</v>
+        <v>1.434957962</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.4141099401590884</v>
+        <v>0.424630769036408</v>
       </c>
       <c r="T71">
-        <v>2.252537745052702</v>
+        <v>2.316881824783938</v>
       </c>
       <c r="U71">
         <v>0.0518</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>12.37859592221897</v>
+        <v>12.20175883761585</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1509582307109224</v>
+        <v>0.1503100799725273</v>
       </c>
       <c r="C72">
-        <v>0.9521927473000735</v>
+        <v>0.9367440403743981</v>
       </c>
       <c r="D72">
-        <v>2.155592747300074</v>
+        <v>2.161164040374398</v>
       </c>
       <c r="E72">
-        <v>0.5594</v>
+        <v>0.58042</v>
       </c>
       <c r="F72">
-        <v>1.4714</v>
+        <v>1.49242</v>
       </c>
       <c r="G72">
         <v>0.268</v>
@@ -7185,28 +7185,28 @@
         <v>0.93</v>
       </c>
       <c r="M72">
-        <v>0.07621852</v>
+        <v>0.07730735600000001</v>
       </c>
       <c r="N72">
-        <v>0.8537814800000001</v>
+        <v>0.852692644</v>
       </c>
       <c r="O72">
-        <v>0.298823518</v>
+        <v>0.2984424254</v>
       </c>
       <c r="P72">
-        <v>0.554957962</v>
+        <v>0.5542502186</v>
       </c>
       <c r="Q72">
-        <v>1.434957962</v>
+        <v>1.4342502186</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.424630769036408</v>
+        <v>0.43587717231906</v>
       </c>
       <c r="T72">
-        <v>2.316881824783938</v>
+        <v>2.385663427255258</v>
       </c>
       <c r="U72">
         <v>0.0518</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>12.20175883761585</v>
+        <v>12.02990307933956</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1503100799725274</v>
+        <v>0.1496619292341324</v>
       </c>
       <c r="C73">
-        <v>0.9367440403743983</v>
+        <v>0.9213242069341094</v>
       </c>
       <c r="D73">
-        <v>2.161164040374398</v>
+        <v>2.16676420693411</v>
       </c>
       <c r="E73">
-        <v>0.5804199999999998</v>
+        <v>0.6014399999999999</v>
       </c>
       <c r="F73">
-        <v>1.49242</v>
+        <v>1.51344</v>
       </c>
       <c r="G73">
         <v>0.268</v>
@@ -7267,28 +7267,28 @@
         <v>0.93</v>
       </c>
       <c r="M73">
-        <v>0.07730735599999999</v>
+        <v>0.07839619199999999</v>
       </c>
       <c r="N73">
-        <v>0.852692644</v>
+        <v>0.851603808</v>
       </c>
       <c r="O73">
-        <v>0.2984424254</v>
+        <v>0.2980613328</v>
       </c>
       <c r="P73">
-        <v>0.5542502186</v>
+        <v>0.5535424752</v>
       </c>
       <c r="Q73">
-        <v>1.4342502186</v>
+        <v>1.4335424752</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.4358771723190599</v>
+        <v>0.4479268901219012</v>
       </c>
       <c r="T73">
-        <v>2.385663427255257</v>
+        <v>2.459358001331672</v>
       </c>
       <c r="U73">
         <v>0.0518</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>12.02990307933957</v>
+        <v>11.86282109212652</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1496619292341324</v>
+        <v>0.1490137784957373</v>
       </c>
       <c r="C74">
-        <v>0.9213242069341094</v>
+        <v>0.9059334720196193</v>
       </c>
       <c r="D74">
-        <v>2.16676420693411</v>
+        <v>2.172393472019619</v>
       </c>
       <c r="E74">
-        <v>0.6014399999999999</v>
+        <v>0.6224599999999999</v>
       </c>
       <c r="F74">
-        <v>1.51344</v>
+        <v>1.53446</v>
       </c>
       <c r="G74">
         <v>0.268</v>
@@ -7349,28 +7349,28 @@
         <v>0.93</v>
       </c>
       <c r="M74">
-        <v>0.07839619199999999</v>
+        <v>0.079485028</v>
       </c>
       <c r="N74">
-        <v>0.851603808</v>
+        <v>0.850514972</v>
       </c>
       <c r="O74">
-        <v>0.2980613328</v>
+        <v>0.2976802402</v>
       </c>
       <c r="P74">
-        <v>0.5535424752</v>
+        <v>0.5528347318</v>
       </c>
       <c r="Q74">
-        <v>1.4335424752</v>
+        <v>1.4328347318</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.4479268901219012</v>
+        <v>0.4608691796138419</v>
       </c>
       <c r="T74">
-        <v>2.459358001331672</v>
+        <v>2.53851143274708</v>
       </c>
       <c r="U74">
         <v>0.0518</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>11.86282109212652</v>
+        <v>11.70031669360423</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1490137784957373</v>
+        <v>0.1483656277573423</v>
       </c>
       <c r="C75">
-        <v>0.9059334720196193</v>
+        <v>0.8905720630160563</v>
       </c>
       <c r="D75">
-        <v>2.172393472019619</v>
+        <v>2.178052063016056</v>
       </c>
       <c r="E75">
-        <v>0.6224599999999999</v>
+        <v>0.6434799999999999</v>
       </c>
       <c r="F75">
-        <v>1.53446</v>
+        <v>1.55548</v>
       </c>
       <c r="G75">
         <v>0.268</v>
@@ -7431,28 +7431,28 @@
         <v>0.93</v>
       </c>
       <c r="M75">
-        <v>0.079485028</v>
+        <v>0.080573864</v>
       </c>
       <c r="N75">
-        <v>0.850514972</v>
+        <v>0.8494261360000001</v>
       </c>
       <c r="O75">
-        <v>0.2976802402</v>
+        <v>0.2972991476</v>
       </c>
       <c r="P75">
-        <v>0.5528347318</v>
+        <v>0.5521269884000001</v>
       </c>
       <c r="Q75">
-        <v>1.4328347318</v>
+        <v>1.4321269884</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.4608691796138419</v>
+        <v>0.474807029835932</v>
       </c>
       <c r="T75">
-        <v>2.53851143274708</v>
+        <v>2.623753589655982</v>
       </c>
       <c r="U75">
         <v>0.0518</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>11.70031669360423</v>
+        <v>11.54220430585283</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1483656277573423</v>
+        <v>0.1477174770189473</v>
       </c>
       <c r="C76">
-        <v>0.8905720630160563</v>
+        <v>0.8752402096838821</v>
       </c>
       <c r="D76">
-        <v>2.178052063016056</v>
+        <v>2.183740209683882</v>
       </c>
       <c r="E76">
-        <v>0.6434799999999999</v>
+        <v>0.6644999999999998</v>
       </c>
       <c r="F76">
-        <v>1.55548</v>
+        <v>1.5765</v>
       </c>
       <c r="G76">
         <v>0.268</v>
@@ -7513,28 +7513,28 @@
         <v>0.93</v>
       </c>
       <c r="M76">
-        <v>0.080573864</v>
+        <v>0.08166269999999999</v>
       </c>
       <c r="N76">
-        <v>0.8494261360000001</v>
+        <v>0.8483373000000001</v>
       </c>
       <c r="O76">
-        <v>0.2972991476</v>
+        <v>0.296918055</v>
       </c>
       <c r="P76">
-        <v>0.5521269884000001</v>
+        <v>0.5514192450000001</v>
       </c>
       <c r="Q76">
-        <v>1.4321269884</v>
+        <v>1.431419245</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.474807029835932</v>
+        <v>0.4898599080757894</v>
       </c>
       <c r="T76">
-        <v>2.623753589655982</v>
+        <v>2.715815119117595</v>
       </c>
       <c r="U76">
         <v>0.0518</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>11.54220430585283</v>
+        <v>11.38830824844146</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1477174770189473</v>
+        <v>0.1470693262805524</v>
       </c>
       <c r="C77">
-        <v>0.8752402096838821</v>
+        <v>0.8599381441899889</v>
       </c>
       <c r="D77">
-        <v>2.183740209683882</v>
+        <v>2.189458144189989</v>
       </c>
       <c r="E77">
-        <v>0.6644999999999998</v>
+        <v>0.6855199999999998</v>
       </c>
       <c r="F77">
-        <v>1.5765</v>
+        <v>1.59752</v>
       </c>
       <c r="G77">
         <v>0.268</v>
@@ -7595,28 +7595,28 @@
         <v>0.93</v>
       </c>
       <c r="M77">
-        <v>0.08166269999999999</v>
+        <v>0.08275153599999999</v>
       </c>
       <c r="N77">
-        <v>0.8483373000000001</v>
+        <v>0.8472484640000001</v>
       </c>
       <c r="O77">
-        <v>0.296918055</v>
+        <v>0.2965369624</v>
       </c>
       <c r="P77">
-        <v>0.5514192450000001</v>
+        <v>0.5507115016000002</v>
       </c>
       <c r="Q77">
-        <v>1.431419245</v>
+        <v>1.4307115016</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.4898599080757894</v>
+        <v>0.5061671928356348</v>
       </c>
       <c r="T77">
-        <v>2.715815119117595</v>
+        <v>2.81554844270101</v>
       </c>
       <c r="U77">
         <v>0.0518</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>11.38830824844146</v>
+        <v>11.23846208727775</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1470693262805524</v>
+        <v>0.1464211755421573</v>
       </c>
       <c r="C78">
-        <v>0.8599381441899889</v>
+        <v>0.8446661011392904</v>
       </c>
       <c r="D78">
-        <v>2.189458144189989</v>
+        <v>2.19520610113929</v>
       </c>
       <c r="E78">
-        <v>0.6855199999999998</v>
+        <v>0.7065399999999998</v>
       </c>
       <c r="F78">
-        <v>1.59752</v>
+        <v>1.61854</v>
       </c>
       <c r="G78">
         <v>0.268</v>
@@ -7677,28 +7677,28 @@
         <v>0.93</v>
       </c>
       <c r="M78">
-        <v>0.08275153599999999</v>
+        <v>0.083840372</v>
       </c>
       <c r="N78">
-        <v>0.8472484640000001</v>
+        <v>0.8461596280000001</v>
       </c>
       <c r="O78">
-        <v>0.2965369624</v>
+        <v>0.2961558698</v>
       </c>
       <c r="P78">
-        <v>0.5507115016000002</v>
+        <v>0.5500037582000001</v>
       </c>
       <c r="Q78">
-        <v>1.4307115016</v>
+        <v>1.4300037582</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.5061671928356348</v>
+        <v>0.5238925023572059</v>
       </c>
       <c r="T78">
-        <v>2.81554844270101</v>
+        <v>2.923954229204722</v>
       </c>
       <c r="U78">
         <v>0.0518</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>11.23846208727775</v>
+        <v>11.09250803419622</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1464211755421573</v>
+        <v>0.1457730248037623</v>
       </c>
       <c r="C79">
-        <v>0.8446661011392904</v>
+        <v>0.8294243176068048</v>
       </c>
       <c r="D79">
-        <v>2.19520610113929</v>
+        <v>2.200984317606805</v>
       </c>
       <c r="E79">
-        <v>0.7065399999999998</v>
+        <v>0.7275599999999999</v>
       </c>
       <c r="F79">
-        <v>1.61854</v>
+        <v>1.63956</v>
       </c>
       <c r="G79">
         <v>0.268</v>
@@ -7759,28 +7759,28 @@
         <v>0.93</v>
       </c>
       <c r="M79">
-        <v>0.083840372</v>
+        <v>0.08492920799999999</v>
       </c>
       <c r="N79">
-        <v>0.8461596280000001</v>
+        <v>0.845070792</v>
       </c>
       <c r="O79">
-        <v>0.2961558698</v>
+        <v>0.2957747772</v>
       </c>
       <c r="P79">
-        <v>0.5500037582000001</v>
+        <v>0.5492960148</v>
       </c>
       <c r="Q79">
-        <v>1.4300037582</v>
+        <v>1.4292960148</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.5238925023572059</v>
+        <v>0.5432292036534651</v>
       </c>
       <c r="T79">
-        <v>2.923954229204722</v>
+        <v>3.04221508720877</v>
       </c>
       <c r="U79">
         <v>0.0518</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>11.09250803419622</v>
+        <v>10.95029639273217</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1457730248037623</v>
+        <v>0.1451248740653673</v>
       </c>
       <c r="C80">
-        <v>0.8294243176068048</v>
+        <v>0.8142130331702515</v>
       </c>
       <c r="D80">
-        <v>2.200984317606805</v>
+        <v>2.206793033170251</v>
       </c>
       <c r="E80">
-        <v>0.7275599999999999</v>
+        <v>0.7485799999999999</v>
       </c>
       <c r="F80">
-        <v>1.63956</v>
+        <v>1.66058</v>
       </c>
       <c r="G80">
         <v>0.268</v>
@@ -7841,28 +7841,28 @@
         <v>0.93</v>
       </c>
       <c r="M80">
-        <v>0.08492920799999999</v>
+        <v>0.086018044</v>
       </c>
       <c r="N80">
-        <v>0.845070792</v>
+        <v>0.843981956</v>
       </c>
       <c r="O80">
-        <v>0.2957747772</v>
+        <v>0.2953936846</v>
       </c>
       <c r="P80">
-        <v>0.5492960148</v>
+        <v>0.5485882714000001</v>
       </c>
       <c r="Q80">
-        <v>1.4292960148</v>
+        <v>1.4285882714</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.5432292036534651</v>
+        <v>0.5644074955493683</v>
       </c>
       <c r="T80">
-        <v>3.04221508720877</v>
+        <v>3.171738884070348</v>
       </c>
       <c r="U80">
         <v>0.0518</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>10.95029639273217</v>
+        <v>10.81168504598872</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1451248740653673</v>
+        <v>0.1444767233269723</v>
       </c>
       <c r="C81">
-        <v>0.8142130331702515</v>
+        <v>0.7990324899431616</v>
       </c>
       <c r="D81">
-        <v>2.206793033170251</v>
+        <v>2.212632489943162</v>
       </c>
       <c r="E81">
-        <v>0.7485799999999999</v>
+        <v>0.7696</v>
       </c>
       <c r="F81">
-        <v>1.66058</v>
+        <v>1.6816</v>
       </c>
       <c r="G81">
         <v>0.268</v>
@@ -7923,28 +7923,28 @@
         <v>0.93</v>
       </c>
       <c r="M81">
-        <v>0.086018044</v>
+        <v>0.08710688</v>
       </c>
       <c r="N81">
-        <v>0.843981956</v>
+        <v>0.8428931200000001</v>
       </c>
       <c r="O81">
-        <v>0.2953936846</v>
+        <v>0.295012592</v>
       </c>
       <c r="P81">
-        <v>0.5485882714000001</v>
+        <v>0.5478805280000001</v>
       </c>
       <c r="Q81">
-        <v>1.4285882714</v>
+        <v>1.427880528</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.5644074955493683</v>
+        <v>0.5877036166348616</v>
       </c>
       <c r="T81">
-        <v>3.171738884070348</v>
+        <v>3.314215060618083</v>
       </c>
       <c r="U81">
         <v>0.0518</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>10.81168504598872</v>
+        <v>10.67653898291386</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1444767233269723</v>
+        <v>0.1438285725885773</v>
       </c>
       <c r="C82">
-        <v>0.7990324899431616</v>
+        <v>0.7838829326085226</v>
       </c>
       <c r="D82">
-        <v>2.212632489943162</v>
+        <v>2.218502932608522</v>
       </c>
       <c r="E82">
-        <v>0.7696</v>
+        <v>0.79062</v>
       </c>
       <c r="F82">
-        <v>1.6816</v>
+        <v>1.70262</v>
       </c>
       <c r="G82">
         <v>0.268</v>
@@ -8005,28 +8005,28 @@
         <v>0.93</v>
       </c>
       <c r="M82">
-        <v>0.08710688</v>
+        <v>0.08819571599999999</v>
       </c>
       <c r="N82">
-        <v>0.8428931200000001</v>
+        <v>0.8418042840000001</v>
       </c>
       <c r="O82">
-        <v>0.295012592</v>
+        <v>0.2946314994</v>
       </c>
       <c r="P82">
-        <v>0.5478805280000001</v>
+        <v>0.5471727846000001</v>
       </c>
       <c r="Q82">
-        <v>1.427880528</v>
+        <v>1.4271727846</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.5877036166348616</v>
+        <v>0.6134519609925123</v>
       </c>
       <c r="T82">
-        <v>3.314215060618083</v>
+        <v>3.471688729434001</v>
       </c>
       <c r="U82">
         <v>0.0518</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>10.67653898291386</v>
+        <v>10.54472985966802</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1438285725885773</v>
+        <v>0.1431804218501823</v>
       </c>
       <c r="C83">
-        <v>0.7838829326085226</v>
+        <v>0.768764608452948</v>
       </c>
       <c r="D83">
-        <v>2.218502932608522</v>
+        <v>2.224404608452948</v>
       </c>
       <c r="E83">
-        <v>0.79062</v>
+        <v>0.81164</v>
       </c>
       <c r="F83">
-        <v>1.70262</v>
+        <v>1.72364</v>
       </c>
       <c r="G83">
         <v>0.268</v>
@@ -8087,28 +8087,28 @@
         <v>0.93</v>
       </c>
       <c r="M83">
-        <v>0.08819571599999999</v>
+        <v>0.089284552</v>
       </c>
       <c r="N83">
-        <v>0.8418042840000001</v>
+        <v>0.8407154480000001</v>
       </c>
       <c r="O83">
-        <v>0.2946314994</v>
+        <v>0.2942504068</v>
       </c>
       <c r="P83">
-        <v>0.5471727846000001</v>
+        <v>0.5464650412000001</v>
       </c>
       <c r="Q83">
-        <v>1.4271727846</v>
+        <v>1.4264650412</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.6134519609925123</v>
+        <v>0.6420612325010129</v>
       </c>
       <c r="T83">
-        <v>3.471688729434001</v>
+        <v>3.646659472562798</v>
       </c>
       <c r="U83">
         <v>0.0518</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>10.54472985966802</v>
+        <v>10.4161355930867</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1431804218501823</v>
+        <v>0.1425322711117873</v>
       </c>
       <c r="C84">
-        <v>0.768764608452948</v>
+        <v>0.753677767401403</v>
       </c>
       <c r="D84">
-        <v>2.224404608452948</v>
+        <v>2.230337767401403</v>
       </c>
       <c r="E84">
-        <v>0.81164</v>
+        <v>0.8326600000000001</v>
       </c>
       <c r="F84">
-        <v>1.72364</v>
+        <v>1.74466</v>
       </c>
       <c r="G84">
         <v>0.268</v>
@@ -8169,28 +8169,28 @@
         <v>0.93</v>
       </c>
       <c r="M84">
-        <v>0.089284552</v>
+        <v>0.090373388</v>
       </c>
       <c r="N84">
-        <v>0.8407154480000001</v>
+        <v>0.839626612</v>
       </c>
       <c r="O84">
-        <v>0.2942504068</v>
+        <v>0.2938693142</v>
       </c>
       <c r="P84">
-        <v>0.5464650412000001</v>
+        <v>0.5457572978</v>
       </c>
       <c r="Q84">
-        <v>1.4264650412</v>
+        <v>1.4257572978</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.6420612325010129</v>
+        <v>0.6740363006575727</v>
       </c>
       <c r="T84">
-        <v>3.646659472562798</v>
+        <v>3.842215009000867</v>
       </c>
       <c r="U84">
         <v>0.0518</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>10.4161355930867</v>
+        <v>10.29063998353143</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1425322711117873</v>
+        <v>0.1418841203733923</v>
       </c>
       <c r="C85">
-        <v>0.753677767401403</v>
+        <v>0.7386226620524892</v>
       </c>
       <c r="D85">
-        <v>2.230337767401403</v>
+        <v>2.236302662052489</v>
       </c>
       <c r="E85">
-        <v>0.8326600000000001</v>
+        <v>0.8536800000000001</v>
       </c>
       <c r="F85">
-        <v>1.74466</v>
+        <v>1.76568</v>
       </c>
       <c r="G85">
         <v>0.268</v>
@@ -8251,28 +8251,28 @@
         <v>0.93</v>
       </c>
       <c r="M85">
-        <v>0.090373388</v>
+        <v>0.09146222400000001</v>
       </c>
       <c r="N85">
-        <v>0.839626612</v>
+        <v>0.838537776</v>
       </c>
       <c r="O85">
-        <v>0.2938693142</v>
+        <v>0.2934882216</v>
       </c>
       <c r="P85">
-        <v>0.5457572978</v>
+        <v>0.5450495544</v>
       </c>
       <c r="Q85">
-        <v>1.4257572978</v>
+        <v>1.4250495544</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.6740363006575727</v>
+        <v>0.7100082523337021</v>
       </c>
       <c r="T85">
-        <v>3.842215009000867</v>
+        <v>4.062214987493693</v>
       </c>
       <c r="U85">
         <v>0.0518</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>10.29063998353143</v>
+        <v>10.16813236467987</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1418841203733923</v>
+        <v>0.1412359696349973</v>
       </c>
       <c r="C86">
-        <v>0.7386226620524894</v>
+        <v>0.7235995477142865</v>
       </c>
       <c r="D86">
-        <v>2.236302662052489</v>
+        <v>2.242299547714286</v>
       </c>
       <c r="E86">
-        <v>0.8536799999999999</v>
+        <v>0.8746999999999997</v>
       </c>
       <c r="F86">
-        <v>1.76568</v>
+        <v>1.7867</v>
       </c>
       <c r="G86">
         <v>0.268</v>
@@ -8333,28 +8333,28 @@
         <v>0.93</v>
       </c>
       <c r="M86">
-        <v>0.09146222399999999</v>
+        <v>0.09255105999999999</v>
       </c>
       <c r="N86">
-        <v>0.838537776</v>
+        <v>0.83744894</v>
       </c>
       <c r="O86">
-        <v>0.2934882216</v>
+        <v>0.293107129</v>
       </c>
       <c r="P86">
-        <v>0.5450495544</v>
+        <v>0.544341811</v>
       </c>
       <c r="Q86">
-        <v>1.4250495544</v>
+        <v>1.424341811</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.7100082523337018</v>
+        <v>0.7507764642333152</v>
       </c>
       <c r="T86">
-        <v>4.062214987493691</v>
+        <v>4.311548296452227</v>
       </c>
       <c r="U86">
         <v>0.0518</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>10.16813236467987</v>
+        <v>10.04850727803658</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1412359696349973</v>
+        <v>0.1405878188966023</v>
       </c>
       <c r="C87">
-        <v>0.7235995477142865</v>
+        <v>0.708608682440782</v>
       </c>
       <c r="D87">
-        <v>2.242299547714286</v>
+        <v>2.248328682440782</v>
       </c>
       <c r="E87">
-        <v>0.8746999999999997</v>
+        <v>0.8957199999999997</v>
       </c>
       <c r="F87">
-        <v>1.7867</v>
+        <v>1.80772</v>
       </c>
       <c r="G87">
         <v>0.268</v>
@@ -8415,28 +8415,28 @@
         <v>0.93</v>
       </c>
       <c r="M87">
-        <v>0.09255105999999999</v>
+        <v>0.09363989599999999</v>
       </c>
       <c r="N87">
-        <v>0.83744894</v>
+        <v>0.836360104</v>
       </c>
       <c r="O87">
-        <v>0.293107129</v>
+        <v>0.2927260364</v>
       </c>
       <c r="P87">
-        <v>0.544341811</v>
+        <v>0.5436340676</v>
       </c>
       <c r="Q87">
-        <v>1.424341811</v>
+        <v>1.4236340676</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.7507764642333152</v>
+        <v>0.7973687064043021</v>
       </c>
       <c r="T87">
-        <v>4.311548296452227</v>
+        <v>4.596500649547698</v>
       </c>
       <c r="U87">
         <v>0.0518</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>10.04850727803658</v>
+        <v>9.931664170152434</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1405878188966023</v>
+        <v>0.1399396681582073</v>
       </c>
       <c r="C88">
-        <v>0.708608682440782</v>
+        <v>0.6936503270688883</v>
       </c>
       <c r="D88">
-        <v>2.248328682440782</v>
+        <v>2.254390327068888</v>
       </c>
       <c r="E88">
-        <v>0.8957199999999997</v>
+        <v>0.9167399999999998</v>
       </c>
       <c r="F88">
-        <v>1.80772</v>
+        <v>1.82874</v>
       </c>
       <c r="G88">
         <v>0.268</v>
@@ -8497,28 +8497,28 @@
         <v>0.93</v>
       </c>
       <c r="M88">
-        <v>0.09363989599999999</v>
+        <v>0.09472873199999998</v>
       </c>
       <c r="N88">
-        <v>0.836360104</v>
+        <v>0.8352712680000001</v>
       </c>
       <c r="O88">
-        <v>0.2927260364</v>
+        <v>0.2923449438</v>
       </c>
       <c r="P88">
-        <v>0.5436340676</v>
+        <v>0.5429263242000001</v>
       </c>
       <c r="Q88">
-        <v>1.4236340676</v>
+        <v>1.4229263242</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.7973687064043021</v>
+        <v>0.8511289858323636</v>
       </c>
       <c r="T88">
-        <v>4.596500649547698</v>
+        <v>4.925291826196316</v>
       </c>
       <c r="U88">
         <v>0.0518</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>9.931664170152434</v>
+        <v>9.817507110725394</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1399396681582073</v>
+        <v>0.1402639174198123</v>
       </c>
       <c r="C89">
-        <v>0.6936503270688883</v>
+        <v>0.6695937983301503</v>
       </c>
       <c r="D89">
-        <v>2.254390327068888</v>
+        <v>2.25135379833015</v>
       </c>
       <c r="E89">
-        <v>0.9167399999999998</v>
+        <v>0.9377599999999998</v>
       </c>
       <c r="F89">
-        <v>1.82874</v>
+        <v>1.84976</v>
       </c>
       <c r="G89">
         <v>0.268</v>
@@ -8579,45 +8579,45 @@
         <v>0.93</v>
       </c>
       <c r="M89">
-        <v>0.09472873199999998</v>
+        <v>0.09896215999999999</v>
       </c>
       <c r="N89">
-        <v>0.8352712680000001</v>
+        <v>0.83103784</v>
       </c>
       <c r="O89">
-        <v>0.2923449438</v>
+        <v>0.290863244</v>
       </c>
       <c r="P89">
-        <v>0.5429263242000001</v>
+        <v>0.5401745960000001</v>
       </c>
       <c r="Q89">
-        <v>1.4229263242</v>
+        <v>1.420174596</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.8511289858323636</v>
+        <v>0.9138493118317691</v>
       </c>
       <c r="T89">
-        <v>4.925291826196316</v>
+        <v>5.308881532286374</v>
       </c>
       <c r="U89">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V89">
         <v>0.35</v>
       </c>
       <c r="W89">
-        <v>0.03367</v>
+        <v>0.034775</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y89">
-        <v>9.817507110725394</v>
+        <v>9.397531339251286</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1402639174198123</v>
+        <v>0.1396268166814173</v>
       </c>
       <c r="C90">
-        <v>0.6695937983301503</v>
+        <v>0.6545478922232224</v>
       </c>
       <c r="D90">
-        <v>2.25135379833015</v>
+        <v>2.257327892223222</v>
       </c>
       <c r="E90">
-        <v>0.9377599999999998</v>
+        <v>0.9587799999999999</v>
       </c>
       <c r="F90">
-        <v>1.84976</v>
+        <v>1.87078</v>
       </c>
       <c r="G90">
         <v>0.268</v>
@@ -8661,28 +8661,28 @@
         <v>0.93</v>
       </c>
       <c r="M90">
-        <v>0.09896215999999999</v>
+        <v>0.10008673</v>
       </c>
       <c r="N90">
-        <v>0.83103784</v>
+        <v>0.82991327</v>
       </c>
       <c r="O90">
-        <v>0.290863244</v>
+        <v>0.2904696445</v>
       </c>
       <c r="P90">
-        <v>0.5401745960000001</v>
+        <v>0.5394436255</v>
       </c>
       <c r="Q90">
-        <v>1.420174596</v>
+        <v>1.4194436255</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.9138493118317691</v>
+        <v>0.9879733334674299</v>
       </c>
       <c r="T90">
-        <v>5.308881532286374</v>
+        <v>5.762214821301894</v>
       </c>
       <c r="U90">
         <v>0.0535</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>9.397531339251286</v>
+        <v>9.291941099484418</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1396268166814173</v>
+        <v>0.1389897159430223</v>
       </c>
       <c r="C91">
-        <v>0.6545478922232224</v>
+        <v>0.6395337756597499</v>
       </c>
       <c r="D91">
-        <v>2.257327892223222</v>
+        <v>2.26333377565975</v>
       </c>
       <c r="E91">
-        <v>0.9587799999999999</v>
+        <v>0.9797999999999999</v>
       </c>
       <c r="F91">
-        <v>1.87078</v>
+        <v>1.8918</v>
       </c>
       <c r="G91">
         <v>0.268</v>
@@ -8743,28 +8743,28 @@
         <v>0.93</v>
       </c>
       <c r="M91">
-        <v>0.10008673</v>
+        <v>0.1012113</v>
       </c>
       <c r="N91">
-        <v>0.82991327</v>
+        <v>0.8287887</v>
       </c>
       <c r="O91">
-        <v>0.2904696445</v>
+        <v>0.290076045</v>
       </c>
       <c r="P91">
-        <v>0.5394436255</v>
+        <v>0.5387126550000001</v>
       </c>
       <c r="Q91">
-        <v>1.4194436255</v>
+        <v>1.418712655</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.9879733334674299</v>
+        <v>1.076922159430223</v>
       </c>
       <c r="T91">
-        <v>5.762214821301894</v>
+        <v>6.306214768120519</v>
       </c>
       <c r="U91">
         <v>0.0535</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>9.291941099484418</v>
+        <v>9.188697309490147</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1389897159430223</v>
+        <v>0.1383526152046273</v>
       </c>
       <c r="C92">
-        <v>0.6395337756597499</v>
+        <v>0.6245517030559711</v>
       </c>
       <c r="D92">
-        <v>2.26333377565975</v>
+        <v>2.269371703055971</v>
       </c>
       <c r="E92">
-        <v>0.9797999999999999</v>
+        <v>1.00082</v>
       </c>
       <c r="F92">
-        <v>1.8918</v>
+        <v>1.91282</v>
       </c>
       <c r="G92">
         <v>0.268</v>
@@ -8825,28 +8825,28 @@
         <v>0.93</v>
       </c>
       <c r="M92">
-        <v>0.1012113</v>
+        <v>0.10233587</v>
       </c>
       <c r="N92">
-        <v>0.8287887</v>
+        <v>0.8276641300000001</v>
       </c>
       <c r="O92">
-        <v>0.290076045</v>
+        <v>0.2896824455</v>
       </c>
       <c r="P92">
-        <v>0.5387126550000001</v>
+        <v>0.5379816845000001</v>
       </c>
       <c r="Q92">
-        <v>1.418712655</v>
+        <v>1.4179816845</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.076922159430223</v>
+        <v>1.185637391162526</v>
       </c>
       <c r="T92">
-        <v>6.306214768120519</v>
+        <v>6.971103592009951</v>
       </c>
       <c r="U92">
         <v>0.0535</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>9.188697309490147</v>
+        <v>9.087722613781464</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1383526152046273</v>
+        <v>0.1377155144662323</v>
       </c>
       <c r="C93">
-        <v>0.6245517030559711</v>
+        <v>0.6096019315502241</v>
       </c>
       <c r="D93">
-        <v>2.269371703055971</v>
+        <v>2.275441931550224</v>
       </c>
       <c r="E93">
-        <v>1.00082</v>
+        <v>1.02184</v>
       </c>
       <c r="F93">
-        <v>1.91282</v>
+        <v>1.93384</v>
       </c>
       <c r="G93">
         <v>0.268</v>
@@ -8907,28 +8907,28 @@
         <v>0.93</v>
       </c>
       <c r="M93">
-        <v>0.10233587</v>
+        <v>0.10346044</v>
       </c>
       <c r="N93">
-        <v>0.8276641300000001</v>
+        <v>0.8265395600000001</v>
       </c>
       <c r="O93">
-        <v>0.2896824455</v>
+        <v>0.289288846</v>
       </c>
       <c r="P93">
-        <v>0.5379816845000001</v>
+        <v>0.537250714</v>
       </c>
       <c r="Q93">
-        <v>1.4179816845</v>
+        <v>1.417250714</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.185637391162526</v>
+        <v>1.321531430827904</v>
       </c>
       <c r="T93">
-        <v>6.971103592009951</v>
+        <v>7.80221462187174</v>
       </c>
       <c r="U93">
         <v>0.0535</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>9.087722613781464</v>
+        <v>8.988943020153403</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1377155144662323</v>
+        <v>0.1370784137278372</v>
       </c>
       <c r="C94">
-        <v>0.6096019315502241</v>
+        <v>0.5946847210394548</v>
       </c>
       <c r="D94">
-        <v>2.275441931550224</v>
+        <v>2.281544721039455</v>
       </c>
       <c r="E94">
-        <v>1.02184</v>
+        <v>1.04286</v>
       </c>
       <c r="F94">
-        <v>1.93384</v>
+        <v>1.95486</v>
       </c>
       <c r="G94">
         <v>0.268</v>
@@ -8989,28 +8989,28 @@
         <v>0.93</v>
       </c>
       <c r="M94">
-        <v>0.10346044</v>
+        <v>0.10458501</v>
       </c>
       <c r="N94">
-        <v>0.8265395600000001</v>
+        <v>0.8254149900000001</v>
       </c>
       <c r="O94">
-        <v>0.289288846</v>
+        <v>0.2888952465</v>
       </c>
       <c r="P94">
-        <v>0.537250714</v>
+        <v>0.5365197435000001</v>
       </c>
       <c r="Q94">
-        <v>1.417250714</v>
+        <v>1.4165197435</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.321531430827904</v>
+        <v>1.496252338969104</v>
       </c>
       <c r="T94">
-        <v>7.80221462187174</v>
+        <v>8.870785945979753</v>
       </c>
       <c r="U94">
         <v>0.0535</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>8.988943020153403</v>
+        <v>8.892287718861432</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1370784137278372</v>
+        <v>0.1364413129894423</v>
       </c>
       <c r="C95">
-        <v>0.5946847210394548</v>
+        <v>0.5798003342163041</v>
       </c>
       <c r="D95">
-        <v>2.281544721039455</v>
+        <v>2.287680334216304</v>
       </c>
       <c r="E95">
-        <v>1.04286</v>
+        <v>1.06388</v>
       </c>
       <c r="F95">
-        <v>1.95486</v>
+        <v>1.97588</v>
       </c>
       <c r="G95">
         <v>0.268</v>
@@ -9071,28 +9071,28 @@
         <v>0.93</v>
       </c>
       <c r="M95">
-        <v>0.10458501</v>
+        <v>0.10570958</v>
       </c>
       <c r="N95">
-        <v>0.8254149900000001</v>
+        <v>0.8242904200000001</v>
       </c>
       <c r="O95">
-        <v>0.2888952465</v>
+        <v>0.288501647</v>
       </c>
       <c r="P95">
-        <v>0.5365197435000001</v>
+        <v>0.5357887730000001</v>
       </c>
       <c r="Q95">
-        <v>1.4165197435</v>
+        <v>1.415788773</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.496252338969104</v>
+        <v>1.72921354982404</v>
       </c>
       <c r="T95">
-        <v>8.870785945979753</v>
+        <v>10.29554771145711</v>
       </c>
       <c r="U95">
         <v>0.0535</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>8.892287718861432</v>
+        <v>8.797688913341631</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1364413129894423</v>
+        <v>0.1358042122510472</v>
       </c>
       <c r="C96">
-        <v>0.5798003342163041</v>
+        <v>0.5649490366068033</v>
       </c>
       <c r="D96">
-        <v>2.287680334216304</v>
+        <v>2.293849036606804</v>
       </c>
       <c r="E96">
-        <v>1.06388</v>
+        <v>1.0849</v>
       </c>
       <c r="F96">
-        <v>1.97588</v>
+        <v>1.9969</v>
       </c>
       <c r="G96">
         <v>0.268</v>
@@ -9153,28 +9153,28 @@
         <v>0.93</v>
       </c>
       <c r="M96">
-        <v>0.10570958</v>
+        <v>0.10683415</v>
       </c>
       <c r="N96">
-        <v>0.8242904200000001</v>
+        <v>0.8231658500000001</v>
       </c>
       <c r="O96">
-        <v>0.288501647</v>
+        <v>0.2881080475</v>
       </c>
       <c r="P96">
-        <v>0.5357887730000001</v>
+        <v>0.5350578025000001</v>
       </c>
       <c r="Q96">
-        <v>1.415788773</v>
+        <v>1.4150578025</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.72921354982404</v>
+        <v>2.055359245020948</v>
       </c>
       <c r="T96">
-        <v>10.29554771145711</v>
+        <v>12.29021418312541</v>
       </c>
       <c r="U96">
         <v>0.0535</v>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>8.797688913341631</v>
+        <v>8.705081661622245</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1358042122510472</v>
+        <v>0.1351671115126522</v>
       </c>
       <c r="C97">
-        <v>0.5649490366068033</v>
+        <v>0.5501310966086796</v>
       </c>
       <c r="D97">
-        <v>2.293849036606804</v>
+        <v>2.30005109660868</v>
       </c>
       <c r="E97">
-        <v>1.0849</v>
+        <v>1.10592</v>
       </c>
       <c r="F97">
-        <v>1.9969</v>
+        <v>2.01792</v>
       </c>
       <c r="G97">
         <v>0.268</v>
@@ -9235,28 +9235,28 @@
         <v>0.93</v>
       </c>
       <c r="M97">
-        <v>0.10683415</v>
+        <v>0.10795872</v>
       </c>
       <c r="N97">
-        <v>0.8231658500000001</v>
+        <v>0.8220412800000001</v>
       </c>
       <c r="O97">
-        <v>0.2881080475</v>
+        <v>0.287714448</v>
       </c>
       <c r="P97">
-        <v>0.5350578025000001</v>
+        <v>0.5343268320000001</v>
       </c>
       <c r="Q97">
-        <v>1.4150578025</v>
+        <v>1.414326832</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.055359245020948</v>
+        <v>2.544577787816311</v>
       </c>
       <c r="T97">
-        <v>12.29021418312541</v>
+        <v>15.28221389062785</v>
       </c>
       <c r="U97">
         <v>0.0535</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>8.705081661622245</v>
+        <v>8.614403727647012</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1351671115126523</v>
+        <v>0.1345300107742573</v>
       </c>
       <c r="C98">
-        <v>0.5501310966086801</v>
+        <v>0.53534678553028</v>
       </c>
       <c r="D98">
-        <v>2.30005109660868</v>
+        <v>2.30628678553028</v>
       </c>
       <c r="E98">
-        <v>1.10592</v>
+        <v>1.12694</v>
       </c>
       <c r="F98">
-        <v>2.01792</v>
+        <v>2.03894</v>
       </c>
       <c r="G98">
         <v>0.268</v>
@@ -9317,28 +9317,28 @@
         <v>0.93</v>
       </c>
       <c r="M98">
-        <v>0.10795872</v>
+        <v>0.10908329</v>
       </c>
       <c r="N98">
-        <v>0.8220412800000001</v>
+        <v>0.8209167100000001</v>
       </c>
       <c r="O98">
-        <v>0.287714448</v>
+        <v>0.2873208485</v>
       </c>
       <c r="P98">
-        <v>0.5343268320000001</v>
+        <v>0.5335958615</v>
       </c>
       <c r="Q98">
-        <v>1.414326832</v>
+        <v>1.4135958615</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.544577787816304</v>
+        <v>3.359942025808573</v>
       </c>
       <c r="T98">
-        <v>15.28221389062781</v>
+        <v>20.26888006979854</v>
       </c>
       <c r="U98">
         <v>0.0535</v>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>8.614403727647014</v>
+        <v>8.525595441794984</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1345300107742573</v>
+        <v>0.1338929100358622</v>
       </c>
       <c r="C99">
-        <v>0.53534678553028</v>
+        <v>0.5205963776301368</v>
       </c>
       <c r="D99">
-        <v>2.30628678553028</v>
+        <v>2.312556377630137</v>
       </c>
       <c r="E99">
-        <v>1.12694</v>
+        <v>1.14796</v>
       </c>
       <c r="F99">
-        <v>2.03894</v>
+        <v>2.05996</v>
       </c>
       <c r="G99">
         <v>0.268</v>
@@ -9399,28 +9399,28 @@
         <v>0.93</v>
       </c>
       <c r="M99">
-        <v>0.10908329</v>
+        <v>0.11020786</v>
       </c>
       <c r="N99">
-        <v>0.8209167100000001</v>
+        <v>0.8197921400000001</v>
       </c>
       <c r="O99">
-        <v>0.2873208485</v>
+        <v>0.286927249</v>
       </c>
       <c r="P99">
-        <v>0.5335958615</v>
+        <v>0.5328648910000001</v>
       </c>
       <c r="Q99">
-        <v>1.4135958615</v>
+        <v>1.412864891</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.359942025808573</v>
+        <v>4.990670501793108</v>
       </c>
       <c r="T99">
-        <v>20.26888006979854</v>
+        <v>30.24221242813998</v>
       </c>
       <c r="U99">
         <v>0.0535</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>8.525595441794984</v>
+        <v>8.438599569939932</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1338929100358622</v>
+        <v>0.1332558092974672</v>
       </c>
       <c r="C100">
-        <v>0.5205963776301368</v>
+        <v>0.5058801501571755</v>
       </c>
       <c r="D100">
-        <v>2.312556377630137</v>
+        <v>2.318860150157175</v>
       </c>
       <c r="E100">
-        <v>1.14796</v>
+        <v>1.16898</v>
       </c>
       <c r="F100">
-        <v>2.05996</v>
+        <v>2.08098</v>
       </c>
       <c r="G100">
         <v>0.268</v>
@@ -9481,28 +9481,28 @@
         <v>0.93</v>
       </c>
       <c r="M100">
-        <v>0.11020786</v>
+        <v>0.11133243</v>
       </c>
       <c r="N100">
-        <v>0.8197921400000001</v>
+        <v>0.8186675700000001</v>
       </c>
       <c r="O100">
-        <v>0.286927249</v>
+        <v>0.2865336495</v>
       </c>
       <c r="P100">
-        <v>0.5328648910000001</v>
+        <v>0.5321339205000001</v>
       </c>
       <c r="Q100">
-        <v>1.412864891</v>
+        <v>1.4121339205</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.990670501793108</v>
+        <v>9.882855929746716</v>
       </c>
       <c r="T100">
-        <v>30.24221242813998</v>
+        <v>60.16220950316431</v>
       </c>
       <c r="U100">
         <v>0.0535</v>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>8.438599569939932</v>
+        <v>8.35336119044559</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1332558092974672</v>
-      </c>
-      <c r="C101">
-        <v>0.5058801501571755</v>
-      </c>
-      <c r="D101">
-        <v>2.318860150157175</v>
-      </c>
-      <c r="E101">
-        <v>1.16898</v>
-      </c>
-      <c r="F101">
-        <v>2.08098</v>
-      </c>
-      <c r="G101">
-        <v>0.268</v>
-      </c>
-      <c r="H101">
-        <v>1.19</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1.81</v>
-      </c>
-      <c r="K101">
-        <v>0.88</v>
-      </c>
-      <c r="L101">
-        <v>0.93</v>
-      </c>
-      <c r="M101">
-        <v>0.11133243</v>
-      </c>
-      <c r="N101">
-        <v>0.8186675700000001</v>
-      </c>
-      <c r="O101">
-        <v>0.2865336495</v>
-      </c>
-      <c r="P101">
-        <v>0.5321339205000001</v>
-      </c>
-      <c r="Q101">
-        <v>1.4121339205</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>9.882855929746716</v>
-      </c>
-      <c r="T101">
-        <v>60.16220950316431</v>
-      </c>
-      <c r="U101">
-        <v>0.0535</v>
-      </c>
-      <c r="V101">
-        <v>0.35</v>
-      </c>
-      <c r="W101">
-        <v>0.034775</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A1/A+</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>8.35336119044559</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
